--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45734</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45624</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>44364</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45869</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>44406</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45518</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44937</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44613</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>44476</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>44084</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45328</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>44271</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44406</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44187</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44348</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44462</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>44480</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>44406</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>45547</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45210</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>44631</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>44792</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>44729</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>44363</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44812</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45485</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44263</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44911</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44238</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44531</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44403</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>45440</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45056</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45252</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45103</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45328</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>45435</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45677</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44621</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>45357</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>45145</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>44817</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45702</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45289</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45860</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>45027</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>45636</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44806</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45226</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44517</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>44138</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44153</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44349</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>44274</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44218</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44560</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44870</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44238</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44266</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44264</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44256</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44059</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44082</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44505</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44264</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44656</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44522</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44271</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44494</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44267</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44216</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44510</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44466</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44775</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44648</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>44767</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44418</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44774</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44504</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44753</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44285</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44209</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>44216</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44659</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44425</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44525</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44812</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44364</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44648</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44581</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44732</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>44790</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44416</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44623</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>44431</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44690</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44200</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44425</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>44425</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44430</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44216</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44510</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>44396</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44259</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44151</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44614</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>44659</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>44613</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>44530</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>44239</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44258</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>44261</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44237</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>44237</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44272</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44491</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44096</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44812</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44502</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>44354</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44416</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>44416</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44223</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44476</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44530</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44264</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44783</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44425</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44498</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44505</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>44466</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44505</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44224</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44224</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44614</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44416</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44427</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>44454</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44767</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44446</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44326</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44256</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44536</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44679</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44748</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44470</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44316</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44424</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44825</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>44250</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44853</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44245</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>44701</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44256</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44578</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44747</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44466</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44784</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44530</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>44425</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44783</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44804</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44238</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44462</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44420</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44146</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>44537</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44613</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44413</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>44539</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44259</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44239</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>44104</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44474</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44440</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44614</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44137</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44246</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44153</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44708</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44729</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44658</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44713</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44522</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44074.6995949074</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44522</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44882</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44440</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44446</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44224</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44475</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>44537</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44440</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>44862</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44627</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>44531</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44505</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45737.43103009259</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>44719</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45061</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44102</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45761</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45110</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45685</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>44579</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44579</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>45090</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>44456</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>44830</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45370</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45244</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>44425</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>44784</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44783</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>44879</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>44579</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45163</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>44578</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45520</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45435</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45183</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45335</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>44865</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>44363</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45062</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44844</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44893</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45143</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45330</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45069</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44294</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44294</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>44725</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>44364</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45398.425</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45667</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45410</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44881</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44858</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>44200</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45702</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>44830</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45630.55130787037</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>44110</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>44825</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>44197</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45310</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45706</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>44943</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44943</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45440</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>44774</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45076</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45424</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45624</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44968</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45043</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>44880</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>45398</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45229</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44463</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>44462</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44224</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45364</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45288</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>44433</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44881.66858796297</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>44053</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45762.87655092592</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45224</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>45224</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45148</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44784.53177083333</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>45660</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>44430</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>44462</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>44181</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>45419</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44817</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45370</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>44960</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45062</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45721.65471064814</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>44267</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>44517</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45544.41584490741</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>44932</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>44932</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>44053</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>44837</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44859</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>44942</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45762.88390046296</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>44067</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45258</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>44063</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45174</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44067</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45686</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>44812</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>44935.59042824074</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>44774</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>44830</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>44074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>44350</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>44965</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>45540.55361111111</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>44078</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>44425</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45729.40054398148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45729.40241898148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45268.4309375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45288</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44837</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44529</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>44414</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44430</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45170</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44949</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45721.46049768518</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45162</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44082</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45356</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45307</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>44144</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44266</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45107</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45419</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>45713</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>44960</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>44477</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>45106</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>45306</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45603.69104166667</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45082</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44452</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>45040</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44097</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45424</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>44950</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45603</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45350</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>45350</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45161</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>44944</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44530</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>44494</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44364</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44144</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44496</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>44251</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45741</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44623</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>44529</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>44536</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45315</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45098</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45425</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45685</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44579</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>45335</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45279</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45419</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45419</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45159</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>44069</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>44992</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>44138</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>44138</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44978</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45775</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>44497</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45329</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44904</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>44092</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>44525</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45775</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45351</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45352</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45352</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>45352</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44140</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44553</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44980</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>44976</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>45201</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45029</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>44579</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45418</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45418</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>44575</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45148</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>44153</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>44137</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45056</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44384</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32087,7 +32087,7 @@
         <v>44084</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>44546</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45096</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32263,7 +32263,7 @@
         <v>44188</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44056</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45306</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45553</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>44370</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>45452</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45616.67362268519</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>45149</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45173</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>44536</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>45132</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45790</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45148</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44181</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45162</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>45162</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45705</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33733,7 +33733,7 @@
         <v>45524</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>45243</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>45110</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>44575</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44620</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45181</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>45370</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>44581</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45146</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>44896</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>45261</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>45160</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44995</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44430</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>44537</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44957</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45335</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45335</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45329</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>45329</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>45051</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44944</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>45721.64611111111</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>45114</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44146</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44649</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44578</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44936</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44199</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44200</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44200</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45170</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45559</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45559</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44293</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45702</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45075</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>44132</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44132</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44119</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45210</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44199</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44200</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45747</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>45702</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44988</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>45218</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45072</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45218</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44216</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44839</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44840</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44153</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>45713</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>45166</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>44126</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>45153</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>45603</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>44652</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45743.6546875</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45044</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44489</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45547</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44990</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44634</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44784</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45061</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45343</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45187</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45027</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45239</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>44966</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>45110</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>44965.44746527778</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45674</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45258</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>44462</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>45624</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>44958</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45161</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44454</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>45146</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44964</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>44965</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>45037</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>44965</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>44988</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>44649</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>44811</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44810</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>44838</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45143</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>44839</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>45440</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42634,7 +42634,7 @@
         <v>44998</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>44678</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>45033</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45685</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45385</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>44235</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45685</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>44491</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>45672</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43467,7 +43467,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43524,7 +43524,7 @@
         <v>45062</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>44200</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>44725</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>44774</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>44853</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>44246</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>45210</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45705</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>44858</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>44727</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45854.54319444444</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45786</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45854.54884259259</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>44082</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45854</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45854</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45733</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>44200</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>45854.58997685185</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
         <v>45854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>45222</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45461</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44799</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45706</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45705</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44725</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44207</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44209</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>45813</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45289</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45813</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45854</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46179,7 +46179,7 @@
         <v>45741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>44078</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>44078</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46355,7 +46355,7 @@
         <v>44798</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>44755</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45798</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46888,7 +46888,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>44690</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45348</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47126,7 +47126,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>44078</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>45138</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44676</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44363</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44810</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45085</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47954,7 +47954,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45820</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>44375</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48197,7 +48197,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45863</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>44452</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>44057</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>45863.31188657408</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49030,7 +49030,7 @@
         <v>45092</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
         <v>44382</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45216</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>44575</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45820</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49325,7 +49325,7 @@
         <v>45860</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45860</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45545</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>44858</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>45685</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45826</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>44404</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45271</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>44382</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>44757</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>45530</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>45224</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
         <v>45798</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>45855</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>44078</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45205</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>45855</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50572,7 +50572,7 @@
         <v>44364</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>44336</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50686,7 +50686,7 @@
         <v>44425</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>44060</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>44209</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>44783</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45278</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45831</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51437,7 +51437,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>45301</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51732,7 +51732,7 @@
         <v>45628</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>44698</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51851,7 +51851,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>44967</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45603</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45855</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45855</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>44830</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45328</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45524</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>44053</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45855</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>44475</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>44475</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45327</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52798,7 +52798,7 @@
         <v>44960</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>44970</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>44358</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>44082</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>44082</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53145,7 +53145,7 @@
         <v>44880</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>44650</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>44118</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53326,7 +53326,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>44837</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53440,7 +53440,7 @@
         <v>44879</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>44879</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>44419</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
         <v>45001</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>44278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>44278</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>44245</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>44199</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54035,7 +54035,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         <v>44339</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>44812</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54211,7 +54211,7 @@
         <v>44199</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>44199</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54325,7 +54325,7 @@
         <v>44109</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54387,7 +54387,7 @@
         <v>44404</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>44198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54506,7 +54506,7 @@
         <v>44960</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>44938</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45075</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54687,7 +54687,7 @@
         <v>44549.75226851852</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54744,7 +54744,7 @@
         <v>44977</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>44869</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>44371</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>45166.57472222222</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54982,7 +54982,7 @@
         <v>44957.73273148148</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55039,7 +55039,7 @@
         <v>45062</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55096,7 +55096,7 @@
         <v>45555.40415509259</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>45370</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55215,7 +55215,7 @@
         <v>44237</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55277,7 +55277,7 @@
         <v>44445</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55334,7 +55334,7 @@
         <v>45604.60871527778</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55391,7 +55391,7 @@
         <v>44960</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55448,7 +55448,7 @@
         <v>44946</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>45448.52920138889</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55562,7 +55562,7 @@
         <v>45424</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>44959</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>44430</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>44865</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>44379</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>44362</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>44468</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45558.32922453704</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56085,7 +56085,7 @@
         <v>44546</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>44968.38077546296</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>44960.37513888889</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56261,7 +56261,7 @@
         <v>44964.61883101852</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56318,7 +56318,7 @@
         <v>45166</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45474.63457175926</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>44543</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>44593</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>44867</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>44616.86403935185</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45096</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56742,7 +56742,7 @@
         <v>45098</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56799,7 +56799,7 @@
         <v>45098</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56856,7 +56856,7 @@
         <v>45098</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>45029</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>44525.34483796296</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57027,7 +57027,7 @@
         <v>44869</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45070</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57151,7 +57151,7 @@
         <v>44466</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>44217</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57270,7 +57270,7 @@
         <v>44239</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57332,7 +57332,7 @@
         <v>45034</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57389,7 +57389,7 @@
         <v>44976</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>44964.60866898148</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57503,7 +57503,7 @@
         <v>44251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57560,7 +57560,7 @@
         <v>44510</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57617,7 +57617,7 @@
         <v>44334</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57674,7 +57674,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57798,7 +57798,7 @@
         <v>44837</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57855,7 +57855,7 @@
         <v>45564</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57912,7 +57912,7 @@
         <v>45677</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57974,7 +57974,7 @@
         <v>45729.41048611111</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58031,7 +58031,7 @@
         <v>44938.64399305556</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58088,7 +58088,7 @@
         <v>44977</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58150,7 +58150,7 @@
         <v>44509</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58207,7 +58207,7 @@
         <v>45247</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45734</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45624</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>44364</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45869</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>44406</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45518</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44937</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44613</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>44476</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>44084</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45328</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>44271</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44406</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44187</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44348</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44462</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>44480</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>44406</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>45547</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45210</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>44631</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>44792</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>44729</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>44363</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44812</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45485</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44263</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44911</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44238</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44531</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44403</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>45440</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45056</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45252</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45103</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45328</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>45435</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45677</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44621</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>45357</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>45145</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>44817</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45702</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45289</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45860</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>45027</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>45636</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44806</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45226</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44517</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>44138</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44153</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44349</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>44274</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44218</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44560</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44870</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44238</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44266</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44264</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44256</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44059</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44082</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44505</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44264</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44656</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44522</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44271</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44494</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44267</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44216</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44510</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44466</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44775</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44648</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>44767</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44418</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44774</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44504</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44753</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44285</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44209</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>44216</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44659</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44425</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44525</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44812</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44364</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44648</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44581</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44732</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>44790</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44416</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44623</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>44431</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44690</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44200</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44425</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>44425</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44430</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44216</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44510</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>44396</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44259</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44151</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44614</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>44659</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>44613</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>44530</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>44239</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44258</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>44261</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44237</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>44237</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44272</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44491</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44096</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44812</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44502</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>44354</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44416</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>44416</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44223</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44476</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44530</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44264</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44783</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44425</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44498</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44505</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>44466</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44505</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44224</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44224</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44614</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44416</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44427</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>44454</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44767</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44446</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44326</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44256</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44536</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44679</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44748</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44470</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44316</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44424</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44825</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>44250</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44853</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44245</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>44701</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44256</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44578</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44747</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44466</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44784</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44530</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>44425</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44783</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44804</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44238</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44462</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44420</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44146</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>44537</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44613</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44413</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>44539</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44259</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44239</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>44104</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44474</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44440</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44614</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44137</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44246</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44153</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44708</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44729</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44658</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44713</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44522</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44074.6995949074</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44522</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44882</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44440</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44446</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44224</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44475</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>44537</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44440</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>44862</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44627</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>44531</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44505</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45737.43103009259</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>44719</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45061</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44102</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45761</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45110</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45685</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>44579</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44579</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>45090</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>44456</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>44830</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45370</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45244</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>44425</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>44784</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44783</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>44879</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>44579</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45163</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>44578</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45520</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45435</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45183</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45335</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>44865</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>44363</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45062</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44844</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44893</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45143</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45330</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45069</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44294</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44294</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>44725</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>44364</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45398.425</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45667</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45410</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44881</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44858</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>44200</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45702</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>44830</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45630.55130787037</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>44110</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>44825</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>44197</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45310</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45706</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>44943</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44943</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45440</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>44774</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45076</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45424</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45624</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44968</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45043</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>44880</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>45398</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45229</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44463</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>44462</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44224</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45364</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45288</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>44433</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44881.66858796297</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>44053</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45762.87655092592</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45224</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>45224</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45148</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44784.53177083333</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>45660</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>44430</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>44462</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>44181</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>45419</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44817</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45370</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>44960</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45062</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45721.65471064814</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>44267</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>44517</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45544.41584490741</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>44932</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>44932</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>44053</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>44837</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44859</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>44942</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45762.88390046296</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>44067</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45258</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>44063</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45174</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44067</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45686</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>44812</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>44935.59042824074</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>44774</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>44830</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>44074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>44350</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>44965</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>45540.55361111111</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>44078</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>44425</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45729.40054398148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45729.40241898148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45268.4309375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45288</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44837</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44529</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>44414</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44430</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45170</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44949</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45384</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45721.46049768518</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45162</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44082</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45356</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45307</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>44144</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44266</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45107</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45419</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>45713</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>44960</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>44477</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>45106</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>45306</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45603.69104166667</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45082</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44452</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>45040</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44097</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45424</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>44950</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45603</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45350</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>45350</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45161</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>44944</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44530</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>44494</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44364</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44144</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44496</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>44251</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45741</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44623</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>44529</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>44536</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45315</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45098</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45425</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45685</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44579</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>45335</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45279</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45419</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45419</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45159</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>44069</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>44992</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>44138</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>44138</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44978</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45775</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>44497</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45329</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44904</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>44092</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>44525</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45775</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45351</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45352</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45352</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>45352</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44140</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44553</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44980</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>44976</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>45201</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45029</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>44579</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45418</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45418</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>44575</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45148</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>44153</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>44137</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45056</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44384</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32087,7 +32087,7 @@
         <v>44084</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>44546</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45096</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32263,7 +32263,7 @@
         <v>44188</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>44056</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45306</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45553</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>44370</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>45452</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45616.67362268519</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>45149</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45173</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>44536</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>45132</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45790</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45148</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44181</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45162</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>45162</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45705</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33733,7 +33733,7 @@
         <v>45524</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>45243</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>45110</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>44575</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44620</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45181</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>45370</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>44581</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45146</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>44896</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>45261</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>45160</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44995</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44430</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>44537</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44957</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45335</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45335</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45329</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>45329</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>45051</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44944</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>45721.64611111111</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>45114</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44146</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44649</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44578</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44936</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44199</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44200</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44200</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45170</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45559</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45559</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44293</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45702</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45075</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>44132</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44132</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44119</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45210</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44199</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44200</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45747</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>45702</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>44784</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44988</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>45218</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45072</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45218</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44216</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44839</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44840</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44153</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>45713</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>45166</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>44126</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>45153</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>45603</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>44652</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45743.6546875</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45044</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44489</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45547</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44990</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44634</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44784</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45061</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45343</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45187</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45027</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45239</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>44966</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>45110</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>44965.44746527778</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45674</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45258</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>44462</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>45624</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>44958</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45161</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44454</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>45146</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44964</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>44965</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>45037</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>44965</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>44988</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>44649</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>44811</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44810</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>44838</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45143</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>44839</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>45440</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42634,7 +42634,7 @@
         <v>44998</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>44678</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>45033</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45685</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45385</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>44235</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45685</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>44491</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>45672</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43467,7 +43467,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43524,7 +43524,7 @@
         <v>45062</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>44200</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>44725</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>44774</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>44853</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>44246</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>45210</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45705</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>44858</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>44727</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45854.54319444444</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45786</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45854.54884259259</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>44082</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45854</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45854</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45733</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>44200</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>45854.58997685185</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
         <v>45854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>45222</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45461</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44799</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45706</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45705</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44725</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44207</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44209</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>45813</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45289</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45813</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45854</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46179,7 +46179,7 @@
         <v>45741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>44078</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>44078</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46355,7 +46355,7 @@
         <v>44798</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>44755</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45798</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46888,7 +46888,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>44690</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45348</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47126,7 +47126,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>44078</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>45138</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44676</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44363</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44810</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45085</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47954,7 +47954,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45820</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>44375</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48197,7 +48197,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45863</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>44452</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>44057</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>45863.31188657408</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49030,7 +49030,7 @@
         <v>45092</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
         <v>44382</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45216</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>44575</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45820</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49325,7 +49325,7 @@
         <v>45860</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45860</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45545</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>44858</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>45685</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45826</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>44404</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45271</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>44382</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>44757</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>45530</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>45224</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
         <v>45798</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>45855</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>44078</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45205</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>45855</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50572,7 +50572,7 @@
         <v>44364</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>44336</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50686,7 +50686,7 @@
         <v>44425</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>44060</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>44209</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>44783</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45278</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45831</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51437,7 +51437,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>45301</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51732,7 +51732,7 @@
         <v>45628</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>44698</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51851,7 +51851,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>44967</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45603</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45855</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45855</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>44830</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45328</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45524</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>44053</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45855</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>44475</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>44475</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45327</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52798,7 +52798,7 @@
         <v>44960</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>44970</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>44358</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>44082</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>44082</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53145,7 +53145,7 @@
         <v>44880</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>44650</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>44118</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53326,7 +53326,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>44837</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53440,7 +53440,7 @@
         <v>44879</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>44879</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>44419</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
         <v>45001</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>44278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>44278</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>44245</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>44199</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54035,7 +54035,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         <v>44339</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>44812</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54211,7 +54211,7 @@
         <v>44199</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>44199</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54325,7 +54325,7 @@
         <v>44109</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54387,7 +54387,7 @@
         <v>44404</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>44198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54506,7 +54506,7 @@
         <v>44960</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>44938</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45075</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54687,7 +54687,7 @@
         <v>44549.75226851852</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54744,7 +54744,7 @@
         <v>44977</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>44869</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>44371</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>45166.57472222222</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54982,7 +54982,7 @@
         <v>44957.73273148148</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55039,7 +55039,7 @@
         <v>45062</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55096,7 +55096,7 @@
         <v>45555.40415509259</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>45370</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55215,7 +55215,7 @@
         <v>44237</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55277,7 +55277,7 @@
         <v>44445</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55334,7 +55334,7 @@
         <v>45604.60871527778</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55391,7 +55391,7 @@
         <v>44960</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55448,7 +55448,7 @@
         <v>44946</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>45448.52920138889</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55562,7 +55562,7 @@
         <v>45424</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>44959</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>44430</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>44865</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>44379</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>44362</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>44468</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45558.32922453704</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56085,7 +56085,7 @@
         <v>44546</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>44968.38077546296</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>44960.37513888889</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56261,7 +56261,7 @@
         <v>44964.61883101852</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56318,7 +56318,7 @@
         <v>45166</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45474.63457175926</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>44543</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>44593</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>44867</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>44616.86403935185</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45096</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56742,7 +56742,7 @@
         <v>45098</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56799,7 +56799,7 @@
         <v>45098</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56856,7 +56856,7 @@
         <v>45098</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>45029</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>44525.34483796296</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57027,7 +57027,7 @@
         <v>44869</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45070</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57151,7 +57151,7 @@
         <v>44466</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>44217</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57270,7 +57270,7 @@
         <v>44239</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57332,7 +57332,7 @@
         <v>45034</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57389,7 +57389,7 @@
         <v>44976</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>44964.60866898148</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57503,7 +57503,7 @@
         <v>44251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57560,7 +57560,7 @@
         <v>44510</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57617,7 +57617,7 @@
         <v>44334</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57674,7 +57674,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57798,7 +57798,7 @@
         <v>44837</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57855,7 +57855,7 @@
         <v>45564</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57912,7 +57912,7 @@
         <v>45677</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57974,7 +57974,7 @@
         <v>45729.41048611111</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58031,7 +58031,7 @@
         <v>44938.64399305556</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58088,7 +58088,7 @@
         <v>44977</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58150,7 +58150,7 @@
         <v>44509</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58207,7 +58207,7 @@
         <v>45247</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45734</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45624</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>44364</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>44406</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45518</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>44937</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44476</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45328</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>44084</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45335</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44271</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44406</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44187</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44348</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44406</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45547</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44462</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>44480</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44792</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45210</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>44263</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44911</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44631</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>44729</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44363</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44812</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45485</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44238</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44531</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44403</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45328</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45435</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45677</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44621</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45357</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44817</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45702</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>45860</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45289</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45027</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45636</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44806</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45145</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45226</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44517</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>45440</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>45056</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>45252</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>44446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>45103</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>44138</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44153</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44274</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44218</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44349</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44560</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44870</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44238</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>44266</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44264</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44256</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44059</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44082</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44505</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44264</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44656</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44522</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44271</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44494</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44267</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44216</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>44510</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44466</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44775</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44418</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44648</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44767</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44774</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44504</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>44285</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>44209</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>44525</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44216</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>44659</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44812</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44425</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44364</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44648</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44581</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44732</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44790</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44416</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44623</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44431</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44216</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44200</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44690</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44425</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>44425</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>44430</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44259</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44510</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44396</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44614</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44151</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44659</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44613</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44258</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44239</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44237</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44261</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44237</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44272</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44491</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>44096</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44812</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44502</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44354</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44416</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44416</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44223</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44476</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44430</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44530</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44783</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44264</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44425</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44498</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>44505</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>44466</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44505</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>44224</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44224</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44614</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44416</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44427</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44454</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44446</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44662</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>44470</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>44316</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>44825</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44578</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44245</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44747</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>44784</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>44466</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44530</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>44783</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44425</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>44804</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>44420</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44146</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44238</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>44462</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>44613</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>44537</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44413</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44539</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44239</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44440</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>44104</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44474</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>44614</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>44246</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>44137</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44153</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44658</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>44708</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>44729</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44522</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44522</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44713</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44882</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44074.6995949074</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44440</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44224</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>44862</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>44446</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>44537</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44440</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44475</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44531</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>44627</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>44256</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44719</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44505</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44748</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>44830</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>44102</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>44326</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>44536</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>44424</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>44679</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>44250</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45090</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>44256</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45244</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44881</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>44784</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>44783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45170</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44858</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45162</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44082</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>44853</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>44830</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45356</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45307</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>44701</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>44144</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>44266</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45107</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>44825</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44960</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45756</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>45440</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45424</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45335</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45424</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>44950</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44865</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44363</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45040</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45350</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44944</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45398</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>45330</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45350</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45315</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>44530</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>44224</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45685</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44496</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45288</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>44433</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>44251</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45741</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44623</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>44069</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45098</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45425</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>44579</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45775</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45335</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45279</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45419</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45419</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45159</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45775</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45224</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45224</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>44553</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44980</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>44976</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45201</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45029</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44579</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45418</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45418</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44575</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45148</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>44384</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44188</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44546</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45096</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45306</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45452</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45616.67362268519</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45149</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44430</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45790</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45173</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44536</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>45524</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>45132</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45162</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>45162</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45705</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45243</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>44430</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>44575</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>45181</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44581</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>44817</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45160</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>44995</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44267</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45335</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45335</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44517</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45329</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45329</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45114</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44146</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>44649</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>44578</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45170</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45559</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45559</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>44293</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45702</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45075</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44119</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45210</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45747</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44988</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45218</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45802</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44839</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44840</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44153</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45166</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44126</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44837</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44859</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44067</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44063</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45153</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44652</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45743.6546875</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44067</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45044</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44812</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>44634</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45061</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45187</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>44078</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>44425</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>45672</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45674</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>44837</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44949</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44477</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45161</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>45146</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>44452</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45166</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45603</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45161</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45854.54319444444</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>45786</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45854.54884259259</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44649</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44494</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45854</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44364</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44144</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44811</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>45854</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44838</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44839</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45733</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44529</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44536</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45854.58997685185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45854</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45813</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>45685</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45813</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45854</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>44992</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45685</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>44138</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>44138</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>44978</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>44497</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45329</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>44904</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>44092</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>44525</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45741</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45537</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45351</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>45352</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45352</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45352</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44890</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>44140</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>44200</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44725</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44432</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44774</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44853</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45798</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44246</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45162</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44153</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44137</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45056</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44858</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45820</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>44084</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45863</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45222</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45461</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>44799</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45863.31188657408</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45705</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>44725</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45820</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>45860</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45860</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>45553</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>44370</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45826</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>45289</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45798</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>44078</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36754,7 +36754,7 @@
         <v>44078</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45855</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>44181</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>45110</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44690</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45348</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>44620</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45370</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>44363</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44810</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45831</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>44896</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45261</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>44452</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>45855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45092</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44575</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>45855</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44537</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>45271</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>44957</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>44911</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>45278</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45301</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45628</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>44698</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45051</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>44944</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45721.64611111111</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44967</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>45603</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45882.36824074074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>44830</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44936</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>45328</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>44199</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>44200</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>44200</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45524</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40896,7 +40896,7 @@
         <v>44475</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40953,7 +40953,7 @@
         <v>44475</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         <v>44132</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>44132</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45327</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44199</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44200</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44960</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>44970</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>44358</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45702</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>44784</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45218</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41885,7 +41885,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>44082</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>45072</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44082</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>44880</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44216</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44992</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44650</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42408,7 +42408,7 @@
         <v>44118</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>44837</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45713</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44879</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>44879</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44419</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45001</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>44278</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44278</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>44245</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45603</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44199</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43355,7 +43355,7 @@
         <v>44489</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45547</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>44990</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>44784</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>44339</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>44812</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>44199</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43883,7 +43883,7 @@
         <v>44199</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>44109</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44404</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45343</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>44198</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>44960</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44245,7 +44245,7 @@
         <v>45027</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>44938</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>45075</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>44549.75226851852</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>44977</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>44869</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>44966</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45110</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>44965.44746527778</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>44371</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>44812</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45166.57472222222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45258</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>44462</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>44957.73273148148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>45062</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45555.40415509259</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>45624</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>45370</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>44237</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>44958</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>44454</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>44445</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45604.60871527778</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>44964</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>44965</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45037</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>44965</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>44988</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>44960</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>44946</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45143</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45448.52920138889</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45424</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>44959</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45440</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45112</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>44998</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>44678</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45033</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46999,7 +46999,7 @@
         <v>44430</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>45385</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>44235</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>44491</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>44865</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>44379</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45216</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47589,7 +47589,7 @@
         <v>44362</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>44468</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>45558.32922453704</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>44546</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>44968.38077546296</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>44960.37513888889</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>45210</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>44964.61883101852</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45166</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45474.63457175926</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>45705</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>44543</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>44593</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>44867</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>44616.86403935185</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>44727</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>44082</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45096</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45098</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45098</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45098</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>44200</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45029</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>44525.34483796296</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>44869</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45070</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>44466</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45706</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>44217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>44239</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>44207</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>44209</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>45034</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>44976</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>44964.60866898148</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>44251</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>44510</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>44334</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50058,7 +50058,7 @@
         <v>45160</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>45160</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>44755</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>44837</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50296,7 +50296,7 @@
         <v>44078</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>45138</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>44676</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45564</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45677</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>45085</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50705,7 +50705,7 @@
         <v>44375</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>45729.41048611111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>44938.64399305556</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50881,7 +50881,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>44382</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45216</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51057,7 +51057,7 @@
         <v>44977</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>44509</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>45247</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45545</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>45061</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>44858</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>45685</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51533,7 +51533,7 @@
         <v>44404</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
         <v>44382</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>44757</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>45530</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>44579</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>44579</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>45370</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45224</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>44078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45205</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>44364</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52299,7 +52299,7 @@
         <v>44336</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>44579</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52413,7 +52413,7 @@
         <v>45163</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>44425</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>44578</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45520</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45435</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52822,7 +52822,7 @@
         <v>44060</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>45062</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52993,7 +52993,7 @@
         <v>44844</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53055,7 +53055,7 @@
         <v>44893</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45143</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>44209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45737.43103009259</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53350,7 +53350,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53407,7 +53407,7 @@
         <v>44294</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>44294</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45761</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>44725</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53640,7 +53640,7 @@
         <v>44364</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45398.425</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45110</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53811,7 +53811,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53868,7 +53868,7 @@
         <v>45667</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53925,7 +53925,7 @@
         <v>45685</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54044,7 +54044,7 @@
         <v>45410</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54101,7 +54101,7 @@
         <v>44456</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54158,7 +54158,7 @@
         <v>44425</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>44879</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54277,7 +54277,7 @@
         <v>45702</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54339,7 +54339,7 @@
         <v>45630.55130787037</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>44197</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>45310</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45183</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>44774</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45069</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54748,7 +54748,7 @@
         <v>45624</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>44968</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45043</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>44880</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45364</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55157,7 +55157,7 @@
         <v>44200</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>44110</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>44881.66858796297</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45706</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55447,7 +55447,7 @@
         <v>45762.87655092592</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55504,7 +55504,7 @@
         <v>44943</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>44943</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>45148</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>44784.53177083333</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>44181</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55789,7 +55789,7 @@
         <v>45076</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55851,7 +55851,7 @@
         <v>45062</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
         <v>45721.65471064814</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>45544.41584490741</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>45229</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>44463</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56141,7 +56141,7 @@
         <v>44462</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56198,7 +56198,7 @@
         <v>44932</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>44932</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56312,7 +56312,7 @@
         <v>44942</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56369,7 +56369,7 @@
         <v>45762.88390046296</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>45174</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>44935.59042824074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56607,7 +56607,7 @@
         <v>44774</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56664,7 +56664,7 @@
         <v>44830</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45660</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56778,7 +56778,7 @@
         <v>44462</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
         <v>45419</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>44960</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56954,7 +56954,7 @@
         <v>44965</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57016,7 +57016,7 @@
         <v>45540.55361111111</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57078,7 +57078,7 @@
         <v>45729.40054398148</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         <v>45729.40241898148</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45268.4309375</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57249,7 +57249,7 @@
         <v>45288</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57306,7 +57306,7 @@
         <v>44529</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>44414</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>44430</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45384</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45721.46049768518</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57606,7 +57606,7 @@
         <v>45686</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>45419</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>45713</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57782,7 +57782,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57844,7 +57844,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57901,7 +57901,7 @@
         <v>45106</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>45306</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>45603.69104166667</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45734</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45624</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>44364</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>44406</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45518</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>44937</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44476</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45328</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>44084</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45335</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44271</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44406</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44187</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44348</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44406</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45547</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44462</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>44480</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44792</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45210</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>44263</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44911</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44631</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>44729</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44363</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44812</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45485</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44238</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44531</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44403</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45328</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45435</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45677</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44621</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45357</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44817</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45702</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>45860</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45289</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45027</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45636</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44806</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45145</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45226</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44517</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>45440</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>45056</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>45252</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>44446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>45103</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>44138</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44153</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44274</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44218</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44349</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44560</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44870</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44238</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>44266</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44264</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44256</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44059</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44082</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44505</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44264</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44656</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44522</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44271</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44494</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44267</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44216</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>44510</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44466</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44775</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44418</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44648</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44767</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44774</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44504</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>44285</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>44209</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>44525</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44216</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>44659</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44812</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44425</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44364</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44648</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44581</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44732</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44790</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44416</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44623</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44431</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44216</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44200</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44690</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44425</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>44425</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>44430</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44259</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44510</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44396</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44614</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44151</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44659</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44613</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44258</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44239</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44237</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44261</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44237</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44272</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44491</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>44096</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44812</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44502</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44354</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44416</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44416</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44223</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44476</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44430</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44530</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44783</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44264</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44425</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44498</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>44505</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>44466</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44505</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>44224</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44224</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44614</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44416</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44427</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44454</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44446</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44662</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>44470</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>44316</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>44825</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44578</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44245</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44747</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>44784</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>44466</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44530</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>44783</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44425</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>44804</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>44420</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44146</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44238</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>44462</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>44613</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>44537</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44413</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44539</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44239</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44440</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>44104</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44474</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>44614</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>44246</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>44137</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44153</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44658</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>44708</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>44729</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44522</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44522</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44713</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44882</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44074.6995949074</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44440</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44224</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>44862</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>44446</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>44537</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44440</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44475</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44531</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>44627</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>44256</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44719</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44505</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44748</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>44830</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>44102</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>44326</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>44536</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>44424</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>44679</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>44250</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45090</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>44256</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45244</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44881</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>44784</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>44783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45170</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44858</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45162</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44082</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>44853</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>44830</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45356</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45307</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>44701</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>44144</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>44266</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45107</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>44825</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44960</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45756</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>45440</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45424</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45335</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45424</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>44950</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44865</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44363</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45040</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45350</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44944</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45398</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>45330</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45350</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45315</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>44530</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>44224</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45685</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44496</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45288</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>44433</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>44251</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45741</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44623</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>44069</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45098</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45425</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>44579</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45775</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45335</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45279</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45419</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45419</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45159</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45775</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45224</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45224</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>44553</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44980</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>44976</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45201</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45029</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44579</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45418</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45418</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44575</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45148</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>44384</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44188</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44546</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45096</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45306</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45452</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45616.67362268519</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45149</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44430</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45790</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45173</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44536</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>45524</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>45132</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45162</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>45162</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45705</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45243</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>44430</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>44575</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>45181</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44581</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>44817</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45160</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>44995</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44267</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45335</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45335</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44517</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45329</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45329</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45114</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44146</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>44649</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>44578</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45170</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45559</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45559</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>44293</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45702</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45075</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44119</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45210</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45747</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44988</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45218</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45802</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44839</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44840</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44153</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45166</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44126</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44837</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44859</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44067</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44063</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45153</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44652</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45743.6546875</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44067</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45044</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44812</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>44634</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45061</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45187</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>44078</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>44425</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>45672</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45674</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>44837</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44949</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44477</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45161</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>45146</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>44452</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45166</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45603</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45161</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45854.54319444444</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>45786</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45854.54884259259</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44649</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44494</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45854</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44364</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44144</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44811</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>45854</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44838</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44839</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45733</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44529</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44536</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45854.58997685185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45854</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45813</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>45685</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45813</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45854</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>44992</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45685</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>44138</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>44138</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>44978</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>44497</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45329</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>44904</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>44092</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>44525</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45741</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45537</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45351</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>45352</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45352</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45352</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44890</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>44140</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>44200</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44725</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44432</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44774</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44853</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45798</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44246</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45162</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44153</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44137</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45056</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44858</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45820</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>44084</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45863</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45222</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45461</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>44799</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45863.31188657408</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45705</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>44725</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45820</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>45860</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45860</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>45553</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>44370</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45826</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>45289</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45798</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>44078</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36754,7 +36754,7 @@
         <v>44078</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45855</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>44181</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>45110</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44690</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45348</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>44620</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45370</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>44363</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44810</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45831</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>44896</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45261</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>44452</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45855</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>45855</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45092</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44575</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>45855</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44537</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>45271</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>44957</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>44911</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>45278</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45301</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45628</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>44698</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45051</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>44944</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45721.64611111111</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44967</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>45603</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45882.36824074074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>44830</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44936</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>45328</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>44199</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>44200</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>44200</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45524</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40896,7 +40896,7 @@
         <v>44475</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40953,7 +40953,7 @@
         <v>44475</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         <v>44132</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>44132</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45327</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44199</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44200</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44960</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>44970</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>44358</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45702</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>44784</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45218</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41885,7 +41885,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>44082</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>45072</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44082</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>44880</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44216</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44992</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>44650</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42408,7 +42408,7 @@
         <v>44118</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>44837</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45713</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44879</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>44879</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44419</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45001</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>44278</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44278</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>44245</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45603</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44199</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43355,7 +43355,7 @@
         <v>44489</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45547</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>44990</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>44784</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>44339</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>44812</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>44199</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43883,7 +43883,7 @@
         <v>44199</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>44109</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44404</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45343</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>44198</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>44960</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44245,7 +44245,7 @@
         <v>45027</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>44938</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>45075</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>44549.75226851852</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>44977</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>44869</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>44966</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45110</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>44965.44746527778</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>44371</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>44812</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45166.57472222222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45258</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>44462</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>44957.73273148148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>45062</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45555.40415509259</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>45624</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>45370</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>44237</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>44958</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>44454</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>44445</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45604.60871527778</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>44964</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>44965</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45037</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>44965</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>44988</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>44960</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>44946</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45143</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45448.52920138889</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45424</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>44959</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45440</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45112</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>44998</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>44678</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45033</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46999,7 +46999,7 @@
         <v>44430</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>45385</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>44235</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>44491</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>44865</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>44379</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45216</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47589,7 +47589,7 @@
         <v>44362</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>44468</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>45558.32922453704</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>44546</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>44968.38077546296</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>44960.37513888889</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>45210</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>44964.61883101852</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45166</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45474.63457175926</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>45705</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>44543</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>44593</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>44867</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>44616.86403935185</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>44727</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>44082</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45096</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45098</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45098</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45098</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>44200</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45029</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>44525.34483796296</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>44869</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45070</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>44466</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45706</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>44217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>44239</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>44207</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>44209</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>45034</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>44976</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>44964.60866898148</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>44251</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>44510</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>44334</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50058,7 +50058,7 @@
         <v>45160</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>45160</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>44755</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>44837</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50296,7 +50296,7 @@
         <v>44078</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>45138</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>44676</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45564</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45677</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>45085</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50705,7 +50705,7 @@
         <v>44375</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>45729.41048611111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>44938.64399305556</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50881,7 +50881,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>44382</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45216</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51057,7 +51057,7 @@
         <v>44977</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>44509</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>45247</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45545</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>45061</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>44858</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>45685</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51533,7 +51533,7 @@
         <v>44404</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
         <v>44382</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>44757</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>45530</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>44579</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>44579</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>45370</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45224</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>44078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45205</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>44364</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52299,7 +52299,7 @@
         <v>44336</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>44579</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52413,7 +52413,7 @@
         <v>45163</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>44425</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>44578</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45520</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45435</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52822,7 +52822,7 @@
         <v>44060</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>45062</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52993,7 +52993,7 @@
         <v>44844</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53055,7 +53055,7 @@
         <v>44893</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45143</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>44209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45737.43103009259</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53350,7 +53350,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53407,7 +53407,7 @@
         <v>44294</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>44294</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45761</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>44725</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53640,7 +53640,7 @@
         <v>44364</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45398.425</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45110</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53811,7 +53811,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53868,7 +53868,7 @@
         <v>45667</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53925,7 +53925,7 @@
         <v>45685</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54044,7 +54044,7 @@
         <v>45410</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54101,7 +54101,7 @@
         <v>44456</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54158,7 +54158,7 @@
         <v>44425</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>44879</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54277,7 +54277,7 @@
         <v>45702</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54339,7 +54339,7 @@
         <v>45630.55130787037</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>44197</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>45310</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45183</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>44774</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45069</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54748,7 +54748,7 @@
         <v>45624</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>44968</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45043</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>44880</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45364</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55157,7 +55157,7 @@
         <v>44200</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>44110</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>44881.66858796297</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45706</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55447,7 +55447,7 @@
         <v>45762.87655092592</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55504,7 +55504,7 @@
         <v>44943</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>44943</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>45148</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>44784.53177083333</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>44181</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55789,7 +55789,7 @@
         <v>45076</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55851,7 +55851,7 @@
         <v>45062</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
         <v>45721.65471064814</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>45544.41584490741</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>45229</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>44463</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56141,7 +56141,7 @@
         <v>44462</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56198,7 +56198,7 @@
         <v>44932</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>44932</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56312,7 +56312,7 @@
         <v>44942</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56369,7 +56369,7 @@
         <v>45762.88390046296</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>45174</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>44935.59042824074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56607,7 +56607,7 @@
         <v>44774</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56664,7 +56664,7 @@
         <v>44830</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56721,7 +56721,7 @@
         <v>45660</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56778,7 +56778,7 @@
         <v>44462</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
         <v>45419</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>44960</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56954,7 +56954,7 @@
         <v>44965</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57016,7 +57016,7 @@
         <v>45540.55361111111</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57078,7 +57078,7 @@
         <v>45729.40054398148</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         <v>45729.40241898148</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45268.4309375</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57249,7 +57249,7 @@
         <v>45288</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57306,7 +57306,7 @@
         <v>44529</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>44414</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>44430</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45384</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45721.46049768518</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57606,7 +57606,7 @@
         <v>45686</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>45419</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>45713</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57782,7 +57782,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57844,7 +57844,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57901,7 +57901,7 @@
         <v>45106</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>45306</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>45603.69104166667</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45624</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45734</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45869</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>44364</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>44406</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44937</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44613</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45518</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44476</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45335</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>45328</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>44084</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44271</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44406</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44187</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44348</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44631</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44263</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44462</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>45547</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>45210</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44406</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>44812</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44480</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>45485</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>44729</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>44792</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44911</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44238</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44531</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44403</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45357</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44817</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45145</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>45027</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45328</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44806</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>45435</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44517</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45677</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45103</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>45860</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45226</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45056</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44621</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45289</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>45440</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44446</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>45636</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>45252</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44138</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44153</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44274</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44349</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44218</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44560</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44870</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44266</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44264</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44238</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44256</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44082</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44505</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44264</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44656</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44522</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44271</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44494</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44267</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44216</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44466</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44775</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44648</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>44767</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44774</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44504</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44753</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44285</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44216</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44659</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44425</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44525</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44364</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44648</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44732</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44790</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>44623</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>44431</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44216</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44690</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44425</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>44200</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>44425</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44430</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>44510</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44396</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44259</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44151</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44659</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44613</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44530</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44258</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44239</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44237</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44261</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44237</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44272</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44491</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44096</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44812</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44502</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>44354</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44416</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44416</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44223</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44476</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>44430</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>44783</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44530</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44264</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44425</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44498</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44505</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>44466</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44505</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44224</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>44224</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44614</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44416</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44427</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>44454</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44446</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>44767</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44662</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>44326</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44536</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>44256</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44679</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>44748</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>44470</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>44316</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44424</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44825</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44245</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44250</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>44256</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>44853</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>44747</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44701</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44578</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44784</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44530</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>44466</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>44425</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>44783</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>44804</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>44238</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>44462</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>44420</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44146</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44413</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44537</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44539</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44613</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44259</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44474</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>44104</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>44440</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>44246</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44137</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44658</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44239</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44708</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44729</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44522</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44522</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44614</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>44882</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>44713</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44074.6995949074</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>44153</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>44446</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44862</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>44475</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44224</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>44537</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>44627</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44531</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>44440</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>44505</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>44440</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>44102</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>44404</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44463</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44462</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44537</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44719</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44425</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44491</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44938.64399305556</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44893</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>44960</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>44239</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>44783</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>44977</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>44837</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45440</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45352</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45352</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>44830</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44865</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>44110</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44578</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45544.41584490741</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45398.425</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44575</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>44774</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45268.4309375</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45628</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>44181</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>44998</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>45370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44382</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44837</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>44837</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>44988</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45424</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45425</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45310</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44652</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44466</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44950</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44138</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45224</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45224</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>44932</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44932</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45762.88390046296</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45737.43103009259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45162</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45301</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44509</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45110</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45210</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44579</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45706</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45173</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44529</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>44078</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44880</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45143</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45062</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45040</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>45205</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>44525</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>45384</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44957</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>44078</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44837</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>44578</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>44379</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44725</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45352</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44082</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44784</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45112</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44358</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45201</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>44936</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>44839</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44119</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>44445</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>44454</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45721.65471064814</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45258</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45328</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44957.73273148148</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45029</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45288</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>44858</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44992</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44140</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44968</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44198</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44199</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45160</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45160</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45686</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45419</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45419</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>44144</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45604.60871527778</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45329</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45702</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44126</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>44251</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45424</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>44425</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45419</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45306</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45288</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>45166</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45547</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>44616.86403935185</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44995</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>44363</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>45448.52920138889</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45335</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>44978</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45148</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44593</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>44990</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44581</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45148</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44371</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45741</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44968.38077546296</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44132</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44132</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44725</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44966</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44698</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45603</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45603</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44727</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44235</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44549.75226851852</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44433</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45685</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44146</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45029</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45146</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44964</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45061</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45061</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>44579</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44082</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>44084</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45461</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45090</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45210</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45247</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44246</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45244</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>45419</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45343</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45034</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>44830</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45149</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>45153</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>45418</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45418</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45660</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30264,7 +30264,7 @@
         <v>44489</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45603</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44475</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>45743.6546875</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45775</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44529</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45271</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>44069</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44097</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44579</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>44525.34483796296</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>44336</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45398</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45143</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>45558.32922453704</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45159</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>44267</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>44543</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>45540.55361111111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45351</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44825</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>44965</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45775</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>44067</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>45166</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45705</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44188</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45162</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44935.59042824074</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>44384</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45545</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45524</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45348</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45327</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>44812</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45279</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44432</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44960</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>44960</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45435</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44430</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45677</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45161</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44859</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44082</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44879</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45630.55130787037</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45729.41048611111</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>44144</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44623</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>45335</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44879</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44649</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45790</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>45315</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45721.64611111111</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>44209</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44783</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44858</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45163</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>45218</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45166.57472222222</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45160</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44339</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>44942</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44294</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44294</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45056</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>44944</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>45033</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>44430</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45229</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>44067</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44911</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44530</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44959</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45162</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44755</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44938</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44078</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44078</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>45085</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44199</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>44199</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>44199</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44970</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>44216</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45069</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45474.63457175926</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45624</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>44266</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45424</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>44992</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45278</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>44153</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>44896</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>44109</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45721.46049768518</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45161</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>44425</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>44830</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>45530</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>44419</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>44798</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45216</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45674</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44980</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44881</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44976</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44867</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45239</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>44197</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45162</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>45802</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45222</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45043</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>44960.37513888889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45370</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>44575</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45329</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45051</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>44137</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45258</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45146</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45174</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>45307</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40291,7 +40291,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40348,7 +40348,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>44510</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45070</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>44678</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>44812</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>44217</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>44153</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45672</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44579</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45705</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45183</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45082</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44810</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45330</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>45075</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>45854</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45813</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45813</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44725</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>44606</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45110</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>44200</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45854.54319444444</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45854.54884259259</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45854</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45733</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45786</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44620</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44375</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>44879</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45854</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45854.58997685185</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45854</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45741</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45096</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>44811</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>44810</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>44958</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>44082</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>44774</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>44817</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>45166</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44494</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>44237</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>44830</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>45110</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>44430</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45114</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>44965</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>44251</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>44200</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>44456</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>45170</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45798</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45863.31188657408</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45820</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45863</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45685</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>44350</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45559</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45762.87655092592</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>44382</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45820</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>44649</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>44462</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>44944</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>45520</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45729.40054398148</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45729.40241898148</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>44293</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         <v>45860</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>44497</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>44224</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>45553</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44890</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45826</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>44496</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>44774</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45855</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45564</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>44904</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>44838</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45452</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>44839</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>44840</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45855</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45685</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45685</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>44965</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>45831</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48561,7 +48561,7 @@
         <v>45798</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45537</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45667</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45855</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44784</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>45855</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>45756</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49518,7 +49518,7 @@
         <v>44370</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>45855</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>45702</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>44865</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45385</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>45062</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45289</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>44414</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>44536</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45107</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>44960</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>44869</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>44546</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>44362</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45524</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45440</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>45350</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>44853</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>44976</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45335</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>44880</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45356</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45096</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>44536</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>44074</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>44452</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>44676</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>44334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>44209</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45370</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51915,7 +51915,7 @@
         <v>45713</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>44784</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>45098</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>45098</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>44553</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>44199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52267,7 +52267,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>44960</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>45559</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52495,7 +52495,7 @@
         <v>45882.36824074074</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45370</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>44690</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>44078</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52842,7 +52842,7 @@
         <v>44881.66858796297</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52956,7 +52956,7 @@
         <v>44757</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>44245</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>44988</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>45181</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45329</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53251,7 +53251,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53365,7 +53365,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53427,7 +53427,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45603.69104166667</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45747</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53665,7 +53665,7 @@
         <v>45216</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53722,7 +53722,7 @@
         <v>45702</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>44452</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53841,7 +53841,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53898,7 +53898,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>44964.60866898148</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>45350</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54240,7 +54240,7 @@
         <v>44092</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54302,7 +54302,7 @@
         <v>44964.61883101852</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>45713</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54421,7 +54421,7 @@
         <v>45170</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>44949</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45555.40415509259</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>44784.53177083333</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54711,7 +54711,7 @@
         <v>44462</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45888</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>44546</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>44200</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>44634</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45076</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55073,7 +55073,7 @@
         <v>44200</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55130,7 +55130,7 @@
         <v>44200</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55187,7 +55187,7 @@
         <v>44812</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>45072</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55301,7 +55301,7 @@
         <v>44477</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>45705</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>44858</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45860</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>44364</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>44364</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>44575</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55710,7 +55710,7 @@
         <v>45132</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45706</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55896,7 +55896,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55953,7 +55953,7 @@
         <v>44579</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56010,7 +56010,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>45092</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56124,7 +56124,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56181,7 +56181,7 @@
         <v>44118</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56243,7 +56243,7 @@
         <v>45624</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56300,7 +56300,7 @@
         <v>45062</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>44200</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45098</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45306</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>44207</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>44278</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>44278</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45027</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45761</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>44181</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>44363</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>44869</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45261</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>44943</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>44943</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45138</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>44650</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>45364</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>45410</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57569,7 +57569,7 @@
         <v>44430</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57631,7 +57631,7 @@
         <v>45106</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45624</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45734</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45869</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>44364</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>44406</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44937</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44613</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45518</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44476</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45335</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>45328</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>44084</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44271</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44406</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44187</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44348</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44631</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44263</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44462</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>45547</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>45210</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44406</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>44812</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44480</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>45485</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>44729</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>44792</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44911</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44238</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44531</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44403</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45357</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44817</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45145</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>45027</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45328</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44806</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>45435</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44517</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45677</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45103</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>45860</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45226</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45056</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44621</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45289</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>45440</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44446</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>45636</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>45252</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44138</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44153</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44274</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44349</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44218</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44560</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44870</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44266</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44264</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44238</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44256</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44082</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44505</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44264</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44656</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44522</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44271</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44494</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44267</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44216</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44466</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44775</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44648</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>44767</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44774</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44504</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44753</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44285</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44216</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44659</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44425</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44525</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44364</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44648</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44732</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44790</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>44623</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>44431</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44216</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44690</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44425</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>44200</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>44425</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44430</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>44510</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44396</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44259</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44151</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44659</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44613</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44530</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44258</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44239</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44237</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44261</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44237</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44272</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44491</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44096</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44812</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44502</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>44354</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44416</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44416</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44223</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44476</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>44430</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>44783</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44530</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44264</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44425</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44498</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44505</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>44466</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44505</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44224</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>44224</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44614</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44416</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44427</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>44454</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44446</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>44767</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44662</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>44326</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44536</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>44256</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44679</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>44748</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>44470</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>44316</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44424</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44825</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44245</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44250</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>44256</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>44853</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>44747</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44701</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44578</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44784</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44530</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>44466</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>44425</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>44783</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>44804</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>44238</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>44462</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>44420</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44146</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44413</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44537</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44539</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44613</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44259</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44474</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>44104</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>44440</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>44246</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44137</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44658</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44239</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44708</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44729</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44522</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44522</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44614</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>44882</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>44713</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44074.6995949074</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>44153</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>44446</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44862</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>44475</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44224</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>44537</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>44627</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44531</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>44440</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>44505</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>44440</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>44102</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>44404</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44463</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44462</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44537</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44719</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44425</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44491</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44938.64399305556</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44893</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>44960</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>44239</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>44783</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>44977</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>44837</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45440</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45352</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45352</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>44830</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44865</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>44110</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44578</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45544.41584490741</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45398.425</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44575</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>44774</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45268.4309375</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45628</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>44181</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>44998</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45062</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>45370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44382</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44837</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>44837</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>44988</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45424</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45425</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45310</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44652</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44466</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44950</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44977</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44138</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>44138</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45224</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45224</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>44932</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44932</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45762.88390046296</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45737.43103009259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45162</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45301</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44509</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45110</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45210</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44579</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45706</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45173</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44529</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>44078</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44880</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45143</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45062</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45040</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>45205</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>44525</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>45384</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44957</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>44078</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44837</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>44578</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>44379</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44725</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45352</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44082</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44784</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45112</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44358</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45201</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>44936</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>44839</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44119</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>44445</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>44454</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45721.65471064814</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45258</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45328</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44957.73273148148</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45029</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45288</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>44858</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44992</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44140</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44968</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44198</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44199</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45160</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45160</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45686</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45419</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45419</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>44144</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45604.60871527778</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45329</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45702</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44126</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>44251</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45424</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>44425</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45419</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45306</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45288</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>45166</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45547</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>44616.86403935185</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44995</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>44363</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>45448.52920138889</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45335</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>44978</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45148</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44593</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>44990</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44581</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45148</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44371</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45741</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44968.38077546296</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44132</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44132</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44725</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44966</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44698</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45603</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45603</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44727</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44235</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44549.75226851852</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44433</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45685</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44146</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45029</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45146</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44964</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45061</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45061</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>44579</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44082</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>44084</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45461</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45090</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45210</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45247</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44246</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45244</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>45419</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45343</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45034</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>44830</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45149</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>45153</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>45418</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45418</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45660</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30264,7 +30264,7 @@
         <v>44489</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45603</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44475</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>45743.6546875</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45775</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44529</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45271</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>44069</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44097</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44579</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>44525.34483796296</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>44336</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45398</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45143</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>45558.32922453704</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45159</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>44267</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>44543</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>45540.55361111111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45351</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44825</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>44965</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45775</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>44067</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>45166</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45705</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44188</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45162</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44935.59042824074</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>44384</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45545</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45524</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45348</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45327</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>44812</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45279</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44432</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44960</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>44960</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45435</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44430</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45677</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45161</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44859</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44082</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44879</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45630.55130787037</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45729.41048611111</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>44144</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44623</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>45335</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44879</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44649</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45790</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>45315</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45721.64611111111</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>44209</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44783</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44858</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45163</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>45218</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45166.57472222222</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45160</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44339</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>44942</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44294</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44294</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45056</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>44944</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>45033</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>44430</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45229</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>44067</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44911</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44530</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44959</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45162</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44755</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44938</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44078</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44078</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>45085</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44199</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>44199</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>44199</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44970</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>44216</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45069</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45474.63457175926</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45624</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>44266</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45424</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>44992</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45278</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>44153</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>44896</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>44109</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45721.46049768518</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45161</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>44425</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>44830</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>45530</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>44419</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>44798</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45216</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45674</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>44799</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44980</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44881</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44976</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44867</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45239</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>44197</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45162</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>45802</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45222</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45043</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>44960.37513888889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45370</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>44575</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45329</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45051</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>44137</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45258</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45146</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45174</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>45307</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40291,7 +40291,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40348,7 +40348,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>44510</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45070</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>44678</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>44812</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>44217</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>44153</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45672</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44579</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45705</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45183</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45082</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44810</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45330</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>45075</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>45854</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45813</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45813</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44725</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>44606</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45110</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>44200</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45854.54319444444</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45854.54884259259</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45854</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45733</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45786</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44620</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44375</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>44879</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45854</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45854.58997685185</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45854</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45741</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45096</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>44811</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>44810</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>44958</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>44082</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>44774</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>44817</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>45166</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44494</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>44237</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>44830</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>45110</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>44430</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45114</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>44965</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>44251</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>44200</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>44456</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>45170</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45798</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45863.31188657408</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45820</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45863</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45685</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>44350</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45559</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45762.87655092592</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>44382</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45820</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>44649</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>44462</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>44944</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>45520</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45729.40054398148</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45729.40241898148</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>44293</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         <v>45860</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>44497</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>44224</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>45553</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44890</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45826</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>44496</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>44774</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45855</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45564</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>44904</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>44838</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45452</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>44839</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>44840</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45855</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45685</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45685</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>44965</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>45831</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48561,7 +48561,7 @@
         <v>45798</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45537</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45667</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45855</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44784</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>45855</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>45756</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49518,7 +49518,7 @@
         <v>44370</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>45855</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>45702</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>44865</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45385</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>45062</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45289</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>44414</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>44536</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45107</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>44960</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>44869</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>44546</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>44362</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45524</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45440</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>45350</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>44853</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>44976</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45335</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>44880</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45356</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45096</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>44536</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>44074</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>44452</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>44676</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>44334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>44209</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45370</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51915,7 +51915,7 @@
         <v>45713</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>44784</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>45098</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>45098</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>44553</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>44199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52267,7 +52267,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>44960</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>45559</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52495,7 +52495,7 @@
         <v>45882.36824074074</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45370</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>44690</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>44078</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52842,7 +52842,7 @@
         <v>44881.66858796297</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52956,7 +52956,7 @@
         <v>44757</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>44245</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>44988</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>45181</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45329</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53251,7 +53251,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53365,7 +53365,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53427,7 +53427,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45603.69104166667</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45747</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53665,7 +53665,7 @@
         <v>45216</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53722,7 +53722,7 @@
         <v>45702</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>44452</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53841,7 +53841,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53898,7 +53898,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>44964.60866898148</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>45350</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54240,7 +54240,7 @@
         <v>44092</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54302,7 +54302,7 @@
         <v>44964.61883101852</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>45713</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54421,7 +54421,7 @@
         <v>45170</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>44949</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45555.40415509259</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>44784.53177083333</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54711,7 +54711,7 @@
         <v>44462</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45888</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>44546</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>44200</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>44634</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45076</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55073,7 +55073,7 @@
         <v>44200</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55130,7 +55130,7 @@
         <v>44200</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55187,7 +55187,7 @@
         <v>44812</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>45072</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55301,7 +55301,7 @@
         <v>44477</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>45705</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>44858</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45860</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>44364</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>44364</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>44575</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55710,7 +55710,7 @@
         <v>45132</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45706</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55896,7 +55896,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55953,7 +55953,7 @@
         <v>44579</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56010,7 +56010,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>45092</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56124,7 +56124,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56181,7 +56181,7 @@
         <v>44118</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56243,7 +56243,7 @@
         <v>45624</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56300,7 +56300,7 @@
         <v>45062</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>44200</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45098</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45306</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>44207</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>44278</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>44278</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45027</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45761</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>44181</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>44363</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>44869</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45261</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>44943</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>44943</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45138</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>44650</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>45364</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>45410</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57569,7 +57569,7 @@
         <v>44430</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57631,7 +57631,7 @@
         <v>45106</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45734</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45624</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>44364</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>44406</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45518</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>44937</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44476</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44084</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45328</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45335</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44271</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44406</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44187</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44348</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44406</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45547</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44462</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>44480</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45210</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44792</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>44631</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>44729</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>44363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44812</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44263</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45485</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>44911</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44238</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44531</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44403</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45328</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45435</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45677</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44621</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45860</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45357</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44817</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45289</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45145</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45027</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45636</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44806</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44446</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45103</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>45226</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44517</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>45440</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>45056</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>45252</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44138</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44153</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44274</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44218</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44349</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44560</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44870</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44238</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44266</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44264</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44256</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44082</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44505</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44264</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44656</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44522</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44271</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44494</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44267</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44216</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44466</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44775</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44418</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44648</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>44767</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44774</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>44504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44753</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44285</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44216</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44659</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44525</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44425</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44364</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44732</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44790</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44581</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>44623</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>44431</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44216</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44200</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44425</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>44690</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>44425</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44430</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44259</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44396</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44510</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44151</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44659</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44614</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44613</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44530</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44258</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44239</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44261</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>44237</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44237</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44272</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44491</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44096</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44812</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44502</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>44416</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44416</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44354</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44476</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44430</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44223</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>44530</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44264</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44783</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44425</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44498</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44505</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>44466</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44505</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44224</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>44224</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44614</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44416</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44427</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>44454</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44446</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>44767</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44662</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44470</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>44316</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44825</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>44853</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>44424</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>44701</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>44578</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44250</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44245</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44256</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>44747</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>44784</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>44466</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>44530</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44783</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>44425</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>44804</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>44420</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>44146</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>44613</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44539</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>44238</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>44462</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>44259</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>44413</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>44537</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44440</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44239</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44614</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44474</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>44246</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>44658</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>44104</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>44153</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>44137</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44522</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>44522</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>44882</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>44708</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44729</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44713</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44074.6995949074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>44440</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>44862</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>44224</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>44537</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44440</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>44446</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>44531</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44475</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>44627</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44256</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44719</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>44865</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44505</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>44363</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>44748</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44830</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45330</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44326</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44102</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44536</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>44679</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45170</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45090</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45162</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>45244</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44784</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44783</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>44082</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45356</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45307</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44144</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44266</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45107</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>44881</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44960</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44858</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45756</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44830</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45335</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45424</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>44950</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>44825</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45350</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>44944</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45440</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45424</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45315</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45040</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44097</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45350</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45398</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44530</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45775</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>44496</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44224</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44251</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45741</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>44623</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45775</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45098</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45288</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44433</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45425</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45224</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45224</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44579</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45335</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>44430</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>45279</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45419</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45419</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45159</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44817</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45370</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44384</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44267</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44517</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>44188</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44837</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44859</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>44553</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44980</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44976</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45258</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45201</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45029</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44579</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45418</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45418</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44812</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>44575</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44350</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44078</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>44425</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45790</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45524</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>44546</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45096</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45306</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45452</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>44837</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>44949</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>44430</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45149</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45173</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>44536</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>44477</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45132</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>45162</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45162</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45705</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45243</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44575</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45181</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44581</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45146</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45160</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>44995</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44452</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45603</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45161</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>44494</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>44364</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>44144</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45335</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45335</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>44529</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45329</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>44536</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45329</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45114</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44992</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>44138</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>44138</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>45239</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>44146</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>44649</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>44497</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45329</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44904</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>44578</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>44092</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44525</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45537</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45351</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45352</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45352</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>45352</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>44890</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45170</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>44140</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>44432</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44293</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45802</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45702</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44153</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>44137</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45075</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45056</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>44084</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>44119</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45210</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44370</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>45747</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44606</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44988</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45672</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45218</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44839</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44840</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>44153</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45166</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>44126</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45786</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45153</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>44652</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>45733</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45044</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44634</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45813</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45813</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45061</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>44181</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>45187</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45110</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>44620</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32096,7 +32096,7 @@
         <v>45370</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>44896</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>45261</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45798</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45674</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>44537</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45820</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>44957</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>44911</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45863</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45863.31188657408</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45051</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>44944</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45860</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45721.64611111111</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45161</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45146</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>45826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>44936</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>44199</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>44200</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>44200</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45798</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45166</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>44132</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>44132</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35071,7 +35071,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>44199</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>44200</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>44649</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>44811</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44810</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44838</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45702</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>44784</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>45218</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>44839</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45072</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>44216</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>44992</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45831</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45713</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45685</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45603</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>45685</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>44200</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>44489</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45547</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>44990</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>44774</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44853</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>44784</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>44246</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45162</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45343</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45027</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>44966</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45110</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>44812</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45258</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>44462</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45222</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45461</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44799</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45624</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45705</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>44725</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45882.36824074074</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>44958</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>44454</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44964</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>45289</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>45741</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44078</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44798</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44965</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>44965</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>44988</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>44690</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>45348</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45143</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>44363</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>44810</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>45440</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>45112</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44452</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>44998</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>44678</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45702</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45033</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45385</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44235</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>44491</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>45888</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>45092</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>45062</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44575</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45210</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45271</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>45705</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>45737.43103009259</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44783</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44727</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44082</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>45278</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44200</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45743.6546875</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45741</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45854.54319444444</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45706</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>45301</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         <v>45628</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45820</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>44698</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>45854</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>45854.54884259259</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45854</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45855</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45855</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>45854.58997685185</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>45860</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>45855</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45855</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>44967</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44207</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>44209</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>45603</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45855</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45854</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45854</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45895.52841435185</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>44830</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45328</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>44755</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45524</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>44078</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45897.65988425926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45138</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>44676</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>44475</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>44475</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45085</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>44375</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45327</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>44960</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>44382</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45216</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>44970</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>45545</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>44858</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45685</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>44404</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>44358</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45973,7 +45973,7 @@
         <v>44382</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>44757</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45530</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>44082</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45224</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>44082</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>44880</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>44078</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45205</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>44650</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>44118</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         <v>44364</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>44336</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>44837</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>44425</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>44879</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47143,7 +47143,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>44879</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44419</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45001</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>44209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>44278</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>44278</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>44245</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45761</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45110</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>44199</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>44456</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>44425</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>44879</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>44339</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>44812</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>44199</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48660,7 +48660,7 @@
         <v>44199</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48717,7 +48717,7 @@
         <v>44109</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>44404</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>44198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>44960</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>44938</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45183</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>45075</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>44549.75226851852</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>44977</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>44869</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>44371</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>45069</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>45166.57472222222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>44957.73273148148</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>45062</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49664,7 +49664,7 @@
         <v>45555.40415509259</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45370</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>44237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>44445</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49959,7 +49959,7 @@
         <v>45604.60871527778</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50078,7 +50078,7 @@
         <v>44960</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>44200</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>44946</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>44110</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>45706</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>44943</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>44943</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>45076</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>45448.52920138889</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45424</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>44959</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45229</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>44463</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>44462</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>44430</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>44865</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>44379</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51181,7 +51181,7 @@
         <v>45216</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45660</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>44462</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>45419</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>44362</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>44960</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51528,7 +51528,7 @@
         <v>44468</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>45558.32922453704</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>44546</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51709,7 +51709,7 @@
         <v>44968.38077546296</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         <v>44960.37513888889</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>44964.61883101852</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51880,7 +51880,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>45474.63457175926</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>44543</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>44593</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>44867</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>44616.86403935185</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45096</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45098</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45098</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45098</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45686</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>44525.34483796296</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>44869</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52770,7 +52770,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45070</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52889,7 +52889,7 @@
         <v>44466</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>44217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>44239</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>45034</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>44976</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53184,7 +53184,7 @@
         <v>44964.60866898148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>44251</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53298,7 +53298,7 @@
         <v>44510</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>44334</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45160</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>45160</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53536,7 +53536,7 @@
         <v>44837</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53593,7 +53593,7 @@
         <v>45564</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53650,7 +53650,7 @@
         <v>45677</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53712,7 +53712,7 @@
         <v>45729.41048611111</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>44938.64399305556</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>44977</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>44509</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53945,7 +53945,7 @@
         <v>45247</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54007,7 +54007,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>44579</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>44579</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>45370</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>44579</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54302,7 +54302,7 @@
         <v>45163</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54364,7 +54364,7 @@
         <v>44578</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54421,7 +54421,7 @@
         <v>45520</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>45435</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45062</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>44844</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>44893</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45143</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>44294</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>44294</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54897,7 +54897,7 @@
         <v>44725</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>44364</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45398.425</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>45667</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>45410</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55182,7 +55182,7 @@
         <v>45630.55130787037</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>44197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55296,7 +55296,7 @@
         <v>45310</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>44774</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45624</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>44968</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45043</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>44880</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45364</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>44881.66858796297</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>45762.87655092592</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45148</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>44784.53177083333</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>44181</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45062</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45721.65471064814</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45544.41584490741</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>44932</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>44932</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         <v>44942</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45762.88390046296</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>45174</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>44935.59042824074</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>44774</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>44830</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>44965</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45540.55361111111</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56751,7 +56751,7 @@
         <v>45729.40054398148</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56808,7 +56808,7 @@
         <v>45729.40241898148</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56865,7 +56865,7 @@
         <v>45268.4309375</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>45288</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56979,7 +56979,7 @@
         <v>44529</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57041,7 +57041,7 @@
         <v>44414</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>44430</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45384</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45721.46049768518</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>45419</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45713</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45106</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>45306</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>45603.69104166667</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45734</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45624</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>44364</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>44406</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45518</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>44937</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44476</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44084</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45328</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45335</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44271</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44406</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44187</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44348</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44406</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45547</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44462</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>44480</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45210</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44792</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>44631</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>44729</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>44363</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44812</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44263</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45485</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>44911</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44238</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44531</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44403</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45328</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45435</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45677</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44621</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45860</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45357</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44817</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45289</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45145</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45027</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45636</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44806</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44446</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45103</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>45226</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44517</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>45440</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>45056</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>45252</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44138</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44153</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44274</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44218</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44349</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44560</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44870</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44238</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44266</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44264</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44256</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44082</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44505</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44264</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44656</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44522</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44271</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44494</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44267</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44216</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44466</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44775</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44418</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44648</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>44767</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44774</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>44504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44753</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44285</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44216</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44659</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44525</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44425</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44364</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44732</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44790</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44581</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>44623</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>44431</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44216</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44200</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44425</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>44690</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>44425</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44430</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44259</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44396</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44510</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44151</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44659</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44614</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44613</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44530</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44258</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44239</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44261</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>44237</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44237</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44272</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44491</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44096</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44812</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44502</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>44416</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44416</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44354</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44476</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44430</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44223</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>44530</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44264</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44783</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44425</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44498</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44505</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>44466</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44505</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44224</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>44224</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44614</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44416</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44427</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>44454</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44446</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>44767</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44662</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44470</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>44316</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44825</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>44853</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>44424</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>44701</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>44578</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44250</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44245</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44256</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>44747</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>44784</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>44466</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>44530</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44783</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>44425</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>44804</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>44420</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>44146</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>44613</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44539</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>44238</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>44462</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>44259</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>44413</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>44537</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44440</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44239</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44614</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44474</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>44246</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>44658</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>44104</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>44153</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>44137</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44522</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>44522</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>44882</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>44708</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44729</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44713</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44074.6995949074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>44440</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>44862</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>44224</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>44537</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44440</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>44446</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>44531</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44475</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>44627</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44256</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44719</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>44865</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44505</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>44363</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>44748</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44830</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45330</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44326</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44102</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44536</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>44679</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45170</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45090</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45162</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>45244</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44784</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44783</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>44082</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45356</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45307</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44144</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44266</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45107</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>44881</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44960</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44858</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45756</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44830</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45335</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45424</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>44950</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>44825</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45350</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>44944</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45440</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45424</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45315</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45040</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44097</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45350</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45398</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44530</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45775</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>44496</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44224</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44251</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45741</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>44623</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45775</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45098</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45288</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44433</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45425</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45224</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45224</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44579</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45335</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>44430</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>45279</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45419</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45419</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45159</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44817</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45370</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44384</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44267</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44517</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>44188</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44837</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44859</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>44553</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44980</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44976</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45258</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45201</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45029</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44579</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45418</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45418</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44812</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>44575</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44350</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44078</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>44425</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45790</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45524</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>44546</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45096</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45306</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45452</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>44837</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>44949</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>44430</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45149</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45173</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>44536</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>44477</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45132</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>45162</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45162</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45705</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45243</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44575</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45181</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44581</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45146</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45160</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>44995</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44452</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45603</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45161</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>44494</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>44364</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>44144</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45335</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45335</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>44529</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45329</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>44536</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45329</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45114</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44992</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>44138</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>44138</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>45239</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>44146</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>44649</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>44497</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45329</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44904</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>44578</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>44092</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44525</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45537</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45351</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45352</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45352</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>45352</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>44890</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45170</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>44140</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>44432</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44293</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45802</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45702</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44153</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>44137</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45075</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45056</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>44084</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>44119</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45210</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44370</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>45747</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44606</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44988</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45672</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45218</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44839</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44840</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>44153</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45166</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>44126</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45786</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45153</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>44652</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>45733</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45044</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44634</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45813</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45813</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45061</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>44181</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>45187</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45110</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>44620</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32096,7 +32096,7 @@
         <v>45370</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>44896</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>45261</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45798</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45674</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>44537</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45820</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>44957</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>44911</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45863</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45863.31188657408</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45051</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>44944</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45860</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45721.64611111111</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45161</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45146</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>45826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>44936</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>44199</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>44200</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>44200</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45798</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45166</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>44132</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>44132</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35071,7 +35071,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>44199</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>44200</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>44649</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>44811</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44810</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44838</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45702</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>44784</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>45218</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>44839</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45072</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>44216</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>44992</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45831</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45713</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45685</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45603</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>45685</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>44200</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>44489</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45547</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>44990</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>44774</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44853</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>44784</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>44246</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45162</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45343</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45027</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>44966</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45110</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>44812</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45258</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>44462</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45222</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45461</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44799</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45624</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45705</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>44725</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45882.36824074074</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>44958</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>44454</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44964</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>45289</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>45741</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44078</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44798</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44965</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>44965</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>44988</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>44690</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>45348</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45143</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>44363</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>44810</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>45440</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>45112</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44452</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>44998</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>44678</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45702</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45033</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45385</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44235</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>44491</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>45888</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>45092</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>45062</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44575</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45210</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45271</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>45705</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>45737.43103009259</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44783</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44727</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44082</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>45278</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44200</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45743.6546875</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45741</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45854.54319444444</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45706</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>45301</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         <v>45628</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45820</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>44698</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>45854</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>45854.54884259259</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45854</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45855</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45855</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>45854.58997685185</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>45860</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>45855</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45855</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>44967</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>44207</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>44209</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>45603</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45855</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45854</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45854</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45895.52841435185</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>44830</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45328</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>44755</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45524</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>44078</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45897.65988425926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45138</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>44676</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>44475</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>44475</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45085</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>44375</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45327</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>44960</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>44382</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45216</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>44970</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>45545</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>44858</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45685</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>44404</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>44358</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45973,7 +45973,7 @@
         <v>44382</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>44757</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45530</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>44082</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45224</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>44082</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>44880</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>44078</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45205</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>44650</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>44118</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         <v>44364</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>44336</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>44837</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>44425</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>44879</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47143,7 +47143,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>44879</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44419</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45001</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>44209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>44278</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>44278</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>44245</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45761</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45110</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>44199</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>44456</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>44425</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>44879</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>44339</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>44812</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>44199</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48660,7 +48660,7 @@
         <v>44199</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48717,7 +48717,7 @@
         <v>44109</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>44404</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>44198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>44960</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>44938</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45183</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>45075</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>44549.75226851852</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>44977</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>44869</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>44371</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>45069</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>45166.57472222222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>44957.73273148148</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>45062</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49664,7 +49664,7 @@
         <v>45555.40415509259</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45370</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>44237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>44445</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49959,7 +49959,7 @@
         <v>45604.60871527778</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50078,7 +50078,7 @@
         <v>44960</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>44200</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>44946</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>44110</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>45706</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>44943</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>44943</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>45076</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>45448.52920138889</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45424</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>44959</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45229</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>44463</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>44462</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>44430</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>44865</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>44379</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51181,7 +51181,7 @@
         <v>45216</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45660</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>44462</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>45419</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>44362</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>44960</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51528,7 +51528,7 @@
         <v>44468</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>45558.32922453704</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>44546</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51709,7 +51709,7 @@
         <v>44968.38077546296</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         <v>44960.37513888889</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>44964.61883101852</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51880,7 +51880,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>45474.63457175926</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>44543</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>44593</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>44867</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>44616.86403935185</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45096</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45098</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45098</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45098</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45686</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>44525.34483796296</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>44869</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52770,7 +52770,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45070</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52889,7 +52889,7 @@
         <v>44466</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>44217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>44239</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>45034</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>44976</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53184,7 +53184,7 @@
         <v>44964.60866898148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>44251</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53298,7 +53298,7 @@
         <v>44510</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>44334</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45160</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>45160</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53536,7 +53536,7 @@
         <v>44837</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53593,7 +53593,7 @@
         <v>45564</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53650,7 +53650,7 @@
         <v>45677</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53712,7 +53712,7 @@
         <v>45729.41048611111</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>44938.64399305556</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>44977</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>44509</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53945,7 +53945,7 @@
         <v>45247</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54007,7 +54007,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>44579</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>44579</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>45370</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>44579</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54302,7 +54302,7 @@
         <v>45163</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54364,7 +54364,7 @@
         <v>44578</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54421,7 +54421,7 @@
         <v>45520</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>45435</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45062</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>44844</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>44893</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45143</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>44294</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>44294</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54897,7 +54897,7 @@
         <v>44725</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>44364</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45398.425</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>45667</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>45410</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55182,7 +55182,7 @@
         <v>45630.55130787037</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>44197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55296,7 +55296,7 @@
         <v>45310</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>44774</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45624</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>44968</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45043</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>44880</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45364</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>44881.66858796297</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>45762.87655092592</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45148</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>44784.53177083333</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>44181</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45062</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45721.65471064814</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45544.41584490741</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>44932</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>44932</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         <v>44942</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45762.88390046296</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>45174</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>44935.59042824074</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>44774</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>44830</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>44965</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45540.55361111111</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56751,7 +56751,7 @@
         <v>45729.40054398148</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56808,7 +56808,7 @@
         <v>45729.40241898148</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56865,7 +56865,7 @@
         <v>45268.4309375</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>45288</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56979,7 +56979,7 @@
         <v>44529</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57041,7 +57041,7 @@
         <v>44414</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>44430</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45384</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45721.46049768518</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>45419</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45713</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>45106</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>45306</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>45603.69104166667</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45734</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45624</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45869</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>44364</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>44406</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44937</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44613</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45518</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44476</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>45328</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44084</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>45335</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44271</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>44406</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44187</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44348</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45547</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44363</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44462</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>45210</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>44406</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>44812</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44480</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45485</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44729</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44792</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44911</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>44631</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>44263</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44238</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44531</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44403</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>44817</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45027</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45435</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>44806</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45677</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>44517</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>45103</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>45056</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44621</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>45226</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>45289</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44446</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>45440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45636</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45252</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>45145</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>45357</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45328</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44138</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>44153</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44349</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44274</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44218</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44560</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>44870</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44238</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44266</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>44264</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>44256</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>44082</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>44505</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44264</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44656</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44522</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>44271</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44494</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44267</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>44216</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>44510</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>44466</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44775</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>44648</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>44767</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44774</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>44418</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44504</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>44753</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>44285</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44209</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>44216</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>44659</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44525</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44425</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>44812</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44364</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44732</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44790</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>44416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44623</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44431</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44216</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44690</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44200</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>44425</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>44425</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44430</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44510</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44259</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44396</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44151</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>44614</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44659</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44613</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>44530</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44258</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>44239</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>44261</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44237</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>44272</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>44491</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44237</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>44096</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44812</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44502</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44354</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>44416</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44416</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44476</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>44223</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>44430</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44264</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44530</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44783</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44425</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>44498</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>44505</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44466</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44505</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44224</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>44224</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44614</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44427</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>44416</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44454</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44446</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44767</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>44662</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>44470</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44316</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44825</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44578</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44245</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44747</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44784</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44530</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44466</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>44783</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44425</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44420</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>44613</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44146</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>44539</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>44259</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44239</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44614</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>44440</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>44238</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>44462</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>44537</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>44153</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>44413</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>44104</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>44137</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>44474</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44522</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44522</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44246</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44708</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44729</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44882</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44713</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44862</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>44531</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>44446</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44475</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44224</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>44537</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44440</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>44256</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>44440</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>44627</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>44505</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>44719</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44748</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>44837</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>44102</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44830</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45352</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44463</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44462</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>44326</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44536</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>44424</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44250</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>44256</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44358</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>44679</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>44491</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>44593</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44853</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45201</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44701</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44468</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>44433</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>44246</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45034</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>44839</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44830</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45153</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>44489</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45775</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44698</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45603</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45603</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>44454</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>44727</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>45258</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44235</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44549.75226851852</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>44957.73273148148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>44146</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44992</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45029</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>44198</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44199</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45775</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>45419</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45419</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>45061</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>45061</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>44579</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>44251</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45424</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>44188</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45461</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44865</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44517</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45090</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>44578</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>45210</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>44774</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45268.4309375</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45370</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44382</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44363</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45424</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>45425</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45335</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44978</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45148</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>44384</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45419</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44990</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>44138</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>44138</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45343</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45149</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>44968.38077546296</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45418</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>45418</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>45660</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45603</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45301</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>44475</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>44475</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>44509</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45110</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45210</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45524</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44097</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44579</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44336</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45398</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45143</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45558.32922453704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>44430</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>44579</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44529</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45143</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>45166</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45062</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45205</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44844</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45146</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45790</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44964</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44082</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44084</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45247</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45244</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45348</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45327</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44812</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44529</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>45271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>45279</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44432</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>44960</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44960</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45435</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44525.34483796296</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45630.55130787037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45159</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44267</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44543</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44879</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45540.55361111111</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45351</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44209</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44965</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>44858</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45705</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>44942</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45162</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>44294</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>44294</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>44935.59042824074</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45056</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44944</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45545</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44430</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>44911</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44530</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44959</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45162</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>44755</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>45677</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45161</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>44859</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44082</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44938</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44879</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>45085</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45729.41048611111</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44144</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44623</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45239</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45335</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>44216</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>44649</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>45315</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45721.64611111111</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45069</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45474.63457175926</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45624</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>45163</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45802</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>45218</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45166.57472222222</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>45160</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>44339</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44992</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45033</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45229</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45530</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>44419</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>44798</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45674</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>44799</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>44881</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>44199</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>44199</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>44199</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44970</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44197</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>45222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>44960.37513888889</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44575</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44266</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45424</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45672</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45278</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>44153</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>44896</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>45051</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>44137</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>44109</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45721.46049768518</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45813</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45813</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45161</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45146</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>45174</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>45307</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>44425</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>45733</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45786</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>44153</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44830</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45216</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>44980</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>44976</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>44867</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45330</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45075</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>45798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45820</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45162</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44725</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>45110</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45043</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>44200</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44879</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45096</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>45826</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45370</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36108,7 +36108,7 @@
         <v>45329</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45831</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>44958</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36460,7 +36460,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>44082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45258</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44946</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45166</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>44494</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45882.36824074074</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>44510</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>44237</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45070</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45702</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45110</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>44678</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>44812</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>44217</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44430</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45888</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>44200</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>44456</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45170</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>44579</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>44350</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45705</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45741</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45183</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>45082</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45855</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45743.6546875</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>45737.43103009259</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>45895.52841435185</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45762.87655092592</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45855</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45854</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>45854.54884259259</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45854.54319444444</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>45897.65988425926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45854</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45854.58997685185</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45854</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45854</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45900.33557870371</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45798</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>45900.31365740741</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>45900.34761574074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>44382</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>45855</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45860</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45903.38063657407</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44649</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>45855</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44462</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44944</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>44810</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>45520</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>44293</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45902</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41145,7 +41145,7 @@
         <v>44497</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45905.3440625</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45905.34798611111</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44496</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45820</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>44774</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44620</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45564</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44375</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>45452</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45001</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44811</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44810</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>45863.31188657408</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>45863</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>45685</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>44774</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45685</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>45537</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>44830</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45667</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>44784</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>44965</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>44251</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45098</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45756</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45044</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45685</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>45702</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45385</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45559</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45062</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45289</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43423,7 +43423,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44536</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45107</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>44869</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>44546</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45729.40054398148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>45729.40241898148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>44224</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45553</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>44362</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>44890</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44065,7 +44065,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>44904</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45350</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>44976</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>44838</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>44839</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>44840</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         <v>44965</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>44967</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>44370</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>44865</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>44414</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>44960</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>44452</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45178,7 +45178,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>44334</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>44209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45354,7 +45354,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45411,7 +45411,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>45524</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45525,7 +45525,7 @@
         <v>45440</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>44199</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>44960</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>45559</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>44853</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>45370</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45335</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>44690</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>44880</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46115,7 +46115,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>44757</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>44245</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45356</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45181</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>45096</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>44536</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45329</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45218</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46700,7 +46700,7 @@
         <v>45187</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>44676</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45603.69104166667</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46876,7 +46876,7 @@
         <v>45747</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>45370</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>44452</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>45713</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>44784</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>44553</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>45350</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>45713</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>44949</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>44881.66858796297</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>45243</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45555.40415509259</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>44784.53177083333</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>44462</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>44546</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>44988</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>44200</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>44200</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>44812</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>44477</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45216</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>45705</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>44964.60866898148</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>44364</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44364</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>44092</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>44575</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>44964.61883101852</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45170</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45132</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>44579</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45224</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>44200</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>44634</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49221,7 +49221,7 @@
         <v>44118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>45076</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45062</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>44200</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>45072</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>44858</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45306</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>44207</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>44363</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>44869</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45261</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>45706</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>44425</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44938.64399305556</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50163,7 +50163,7 @@
         <v>44893</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>45092</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50282,7 +50282,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50339,7 +50339,7 @@
         <v>45624</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>45544.41584490741</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>45398.425</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>44575</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45628</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>44181</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50686,7 +50686,7 @@
         <v>45062</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>45098</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>44652</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>44278</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>44278</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>45027</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>45761</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>44181</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>44950</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>44977</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51385,7 +51385,7 @@
         <v>44932</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51442,7 +51442,7 @@
         <v>44932</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>44943</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>44943</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51670,7 +51670,7 @@
         <v>45138</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51727,7 +51727,7 @@
         <v>44650</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51784,7 +51784,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51841,7 +51841,7 @@
         <v>45364</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45706</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>45173</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45410</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>44880</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         <v>44430</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52198,7 +52198,7 @@
         <v>45106</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52255,7 +52255,7 @@
         <v>45040</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52369,7 +52369,7 @@
         <v>44404</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>44404</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>44537</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>44960</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>44239</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>44783</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>44977</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>44837</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45440</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53083,7 +53083,7 @@
         <v>44725</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53140,7 +53140,7 @@
         <v>45352</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53202,7 +53202,7 @@
         <v>45352</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>44110</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53321,7 +53321,7 @@
         <v>44784</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53378,7 +53378,7 @@
         <v>44998</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53435,7 +53435,7 @@
         <v>44837</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>44837</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         <v>44988</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53606,7 +53606,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53663,7 +53663,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>44466</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45224</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>45224</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>45029</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>45288</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54176,7 +54176,7 @@
         <v>44858</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45762.88390046296</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54295,7 +54295,7 @@
         <v>44140</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54352,7 +54352,7 @@
         <v>45162</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>44968</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54466,7 +54466,7 @@
         <v>45160</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>45160</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45686</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45075</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54709,7 +54709,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45702</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>44525</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>45384</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>44957</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>44578</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>44364</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45335</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55455,7 +55455,7 @@
         <v>44379</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>44082</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55569,7 +55569,7 @@
         <v>45306</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55631,7 +55631,7 @@
         <v>45288</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55688,7 +55688,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>45547</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55802,7 +55802,7 @@
         <v>45112</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55859,7 +55859,7 @@
         <v>44995</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55973,7 +55973,7 @@
         <v>45448.52920138889</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56030,7 +56030,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56092,7 +56092,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56154,7 +56154,7 @@
         <v>44581</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>45148</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56330,7 +56330,7 @@
         <v>44371</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56387,7 +56387,7 @@
         <v>45741</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>44132</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>44132</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>44936</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>44119</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56682,7 +56682,7 @@
         <v>44445</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56739,7 +56739,7 @@
         <v>44725</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>44966</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45721.65471064814</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56915,7 +56915,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45328</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>45604.60871527778</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45329</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>44126</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>44425</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57314,7 +57314,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>45419</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>44616.86403935185</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45734</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45624</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44364</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>45869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44406</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>45518</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>44937</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>44476</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>45328</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45335</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>44271</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44406</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>44187</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44348</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>44406</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45547</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44462</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44480</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>45210</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44792</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>44631</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44729</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44363</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>44812</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45485</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>44263</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44911</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44238</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44531</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>44446</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45328</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44403</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45435</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45677</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>44621</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>45357</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44817</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>45289</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>45145</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45027</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45636</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44446</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45103</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44806</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>45226</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44517</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>45440</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45056</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45252</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44138</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44153</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44218</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44349</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>44274</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44560</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44870</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44238</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44256</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>44266</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>44264</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44505</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44264</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44656</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44522</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44271</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44494</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44267</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>44216</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44510</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>44466</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44775</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44418</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>44648</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44767</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>44774</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44504</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>44753</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44285</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>44209</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44216</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44659</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44525</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44425</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44812</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44648</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44364</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44581</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44732</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44790</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44416</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44623</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>44431</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>44216</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44200</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44690</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44425</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>44425</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>44259</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44510</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44396</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>44151</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44614</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44659</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44430</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44530</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44258</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44239</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>44237</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44261</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>44237</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>44272</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>44491</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44096</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>44812</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44502</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>44354</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44416</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>44416</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44223</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44430</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>44530</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44783</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44425</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44498</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44264</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>44505</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>44466</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44505</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44224</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44224</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44614</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>44416</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44427</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>44454</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44767</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>44446</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44662</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44470</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>44853</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>44424</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>44316</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>44701</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>44250</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44825</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44578</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>44256</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44747</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>44466</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44783</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>44804</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44245</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>44146</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44537</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44539</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44420</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44613</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>44530</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44104</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44239</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44137</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44440</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>44425</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>44614</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>44708</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44729</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>44153</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>44658</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>44522</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>44713</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>44522</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44882</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44446</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>44475</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44862</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44440</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44627</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44238</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44462</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44505</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44256</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45335</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44865</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44363</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44102</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44413</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>45330</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44830</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>45090</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>44784</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>44326</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44536</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44881</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>44474</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44679</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44858</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44830</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44825</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45440</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45424</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45170</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45162</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45356</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44246</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45307</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44144</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44266</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45107</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>44960</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45756</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45424</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44950</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45398</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45350</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45082</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45315</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45040</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>44224</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>44097</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45288</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45350</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>44433</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44530</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44496</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45224</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45224</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>44251</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45741</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>44623</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45775</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>44430</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45098</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45775</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45425</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44579</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45335</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>44817</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45370</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         <v>45279</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45419</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45419</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45159</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44267</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>44517</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44553</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>44980</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>44976</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45029</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44837</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>44859</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>44384</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>44579</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>44575</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>44188</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>44812</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>44546</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45096</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45306</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44350</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45452</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45149</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>44425</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>45524</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45173</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>44536</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45132</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>44837</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>44224</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45162</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44537</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45162</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45705</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44440</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>44949</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45243</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>44430</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>44575</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45181</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>44581</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44477</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45160</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44995</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44452</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45335</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45335</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45329</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45329</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45603</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45161</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>44494</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>44364</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44144</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>44719</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45114</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44529</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44536</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44146</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44578</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>45170</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45559</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45559</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44293</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45702</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>44992</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>44748</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45075</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44138</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44138</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44497</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>45329</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44904</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44092</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>44119</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44525</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45210</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45239</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>45537</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45747</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45352</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45352</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45352</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44890</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45218</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44140</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44839</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44840</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44153</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45166</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44432</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>45802</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44126</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45153</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44652</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45044</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44153</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44137</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44634</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45056</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>45061</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45187</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>45553</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>44370</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>45672</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>45674</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>45786</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30846,7 +30846,7 @@
         <v>45733</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44181</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>45161</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>45146</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45110</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44620</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45813</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45813</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45370</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>45166</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44896</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>45261</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45798</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44649</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>44811</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44810</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>44838</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44839</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44537</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>44957</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45820</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45051</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44944</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45685</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45685</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44200</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>44725</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>44774</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44853</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>44246</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45826</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45162</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44936</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44199</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44200</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44200</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>44858</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>45222</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>44132</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>44132</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>45461</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>44799</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>45705</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>44199</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>44200</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44725</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45831</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45702</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>44784</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45218</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>45289</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>44216</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>44992</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45741</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45713</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45603</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>44489</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45547</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>44990</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44784</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45343</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45027</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44690</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45348</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>44966</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45110</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>44363</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>44810</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>44812</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45258</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>44462</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45624</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>44958</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>44454</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>44452</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>44964</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>44965</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>44965</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44988</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45143</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45092</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44575</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45882.36824074074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45440</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45112</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>44998</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>44678</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45033</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45385</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>44235</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44491</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45062</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>45210</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45705</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>44727</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>45271</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>44200</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>44783</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45706</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>45278</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44207</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44209</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44755</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>45301</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45628</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>44698</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45138</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>44676</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45085</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>44967</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>44375</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>45603</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42321,7 +42321,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>44382</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>45216</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45545</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>44858</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45685</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>44404</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>44382</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>44757</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45530</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>45224</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45205</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43149,7 +43149,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>44364</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>44336</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43320,7 +43320,7 @@
         <v>44425</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>44209</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>45761</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45110</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>44456</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>44425</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>44879</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>44830</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45328</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45183</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45524</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45069</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>44475</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>44475</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>44200</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>44110</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45706</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>44943</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44943</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45076</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45327</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>45229</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>44463</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44462</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>44960</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>44970</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>44358</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45660</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>44462</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45419</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45878,7 +45878,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>44960</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46049,7 +46049,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>44880</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45702</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>44650</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>44118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>44837</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>44879</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>44879</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>44419</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45001</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>44278</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>44278</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>44245</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45686</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>44199</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47053,7 +47053,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>44339</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>44812</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>44199</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>44199</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47524,7 +47524,7 @@
         <v>45737.43103009259</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>44109</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>44404</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>44198</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>44960</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>44938</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45075</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>44549.75226851852</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>44977</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>44869</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>45743.6546875</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45741</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>44371</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>45854.54319444444</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45166.57472222222</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45854</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>45854.54884259259</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48538,7 +48538,7 @@
         <v>45854</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>44957.73273148148</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>45854.58997685185</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45062</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45555.40415509259</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45370</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45854</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45854</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45895.52841435185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>44237</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>44445</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45604.60871527778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>44960</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>44946</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45448.52920138889</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45897.65988425926</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45860</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>45424</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>44959</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>45860</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>45900.34761574074</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45900.33557870371</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45900.31365740741</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>44430</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>45903.38063657407</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>44865</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>44379</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>45820</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>45216</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50231,7 +50231,7 @@
         <v>44362</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>44468</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50345,7 +50345,7 @@
         <v>45558.32922453704</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>44546</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         <v>44968.38077546296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>44960.37513888889</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>44964.61883101852</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45166</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45474.63457175926</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45905.3440625</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45905.34798611111</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>44944</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>44543</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>44593</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45863.31188657408</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>45863</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>45908.28657407407</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45908.43563657408</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>44867</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>44616.86403935185</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45096</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45098</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45098</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45098</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45029</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>44525.34483796296</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>44869</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>45070</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>44466</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>44217</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>44239</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45888</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45798</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45902</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45034</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52291,7 +52291,7 @@
         <v>44976</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>44964.60866898148</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>44251</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52462,7 +52462,7 @@
         <v>45855</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52524,7 +52524,7 @@
         <v>45855</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         <v>44510</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>44334</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45160</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52762,7 +52762,7 @@
         <v>45160</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52824,7 +52824,7 @@
         <v>45855</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52886,7 +52886,7 @@
         <v>45855</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45855</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53010,7 +53010,7 @@
         <v>44837</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
         <v>45564</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45677</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53186,7 +53186,7 @@
         <v>45729.41048611111</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53243,7 +53243,7 @@
         <v>44938.64399305556</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53300,7 +53300,7 @@
         <v>44977</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53362,7 +53362,7 @@
         <v>44509</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45061</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53543,7 +53543,7 @@
         <v>44579</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53600,7 +53600,7 @@
         <v>44579</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53657,7 +53657,7 @@
         <v>45370</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53719,7 +53719,7 @@
         <v>44579</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         <v>45163</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>44578</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53895,7 +53895,7 @@
         <v>45520</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>45435</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45062</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>44844</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>44893</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54195,7 +54195,7 @@
         <v>45143</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         <v>44294</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>44294</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54371,7 +54371,7 @@
         <v>44725</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54428,7 +54428,7 @@
         <v>44364</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54485,7 +54485,7 @@
         <v>45398.425</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45667</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54599,7 +54599,7 @@
         <v>45410</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>45630.55130787037</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54713,7 +54713,7 @@
         <v>44197</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54770,7 +54770,7 @@
         <v>45310</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>44774</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45624</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>44968</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>45043</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55060,7 +55060,7 @@
         <v>44880</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55122,7 +55122,7 @@
         <v>45364</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55179,7 +55179,7 @@
         <v>44881.66858796297</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55236,7 +55236,7 @@
         <v>45762.87655092592</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>45148</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55350,7 +55350,7 @@
         <v>44784.53177083333</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>44181</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45062</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45721.65471064814</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55578,7 +55578,7 @@
         <v>45544.41584490741</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55635,7 +55635,7 @@
         <v>44932</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>44932</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>44942</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>45174</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55868,7 +55868,7 @@
         <v>44935.59042824074</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55930,7 +55930,7 @@
         <v>44774</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>44830</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56044,7 +56044,7 @@
         <v>44965</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56106,7 +56106,7 @@
         <v>45540.55361111111</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45729.40054398148</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>45729.40241898148</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45268.4309375</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45288</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>44529</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>44414</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>44430</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45384</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45721.46049768518</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45419</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45713</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56815,7 +56815,7 @@
         <v>45106</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45306</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56929,7 +56929,7 @@
         <v>45603.69104166667</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45540.64393518519</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44434</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>44543</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45244</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>45734</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45624</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44384</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44364</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>45846.66900462963</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>45869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44406</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>45518</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45546.44880787037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>44937</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45540.56883101852</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>44476</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>45448.52262731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45540.61594907408</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>45328</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>45603.68148148148</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45335</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>44271</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44406</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>44187</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44348</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>44406</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45547</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44462</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44480</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>45210</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44792</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>44631</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44729</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44363</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>44812</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45485</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>44263</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44911</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>45540.60987268519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>44873.3884375</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44488.48640046296</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44238</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44531</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>44446</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45385.59928240741</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45328</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44403</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45435</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45677</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>44621</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45813.39127314815</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>45357</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44817</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45832.40953703703</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>45289</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>45145</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45027</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45636</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44446</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45103</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44806</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>45226</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44517</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>45390.67849537037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>45440</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45056</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45252</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>45603.69032407407</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44138</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44153</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44218</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>44285.57488425926</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44349</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44283.88116898148</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>44274</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44560</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44870</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>44811.41642361111</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44238</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44256</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>44266</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>44264</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44505</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44264</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44656</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44522</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44271</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44494</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44267</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>44216</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44510</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>44466</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44310.46975694445</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44775</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>44705.71707175926</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>44418</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>44648</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44767</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>44774</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44733.39394675926</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44504</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>44753</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44873.38078703704</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44285</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44652.44121527778</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>44209</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44216</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44659</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44525</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44425</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44812</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44648</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44364</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44581</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44732</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44790</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44416</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44873.38539351852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44623</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>44705.69604166667</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>44431</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>44216</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44200</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44690</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44425</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>44425</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>44259</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44830.91241898148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44510</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44396</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44804.68011574074</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>44151</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44614</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44659</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44430</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44530</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44258</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44239</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>44237</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44261</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>44237</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>44272</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>44491</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44096</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44676.50108796296</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>44812</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44502</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>44354</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44416</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>44416</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44223</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44430</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>44530</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44783</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44425</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44498</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44264</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>44505</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>44466</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44505</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44224</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44224</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44614</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>44416</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44427</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>44454</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44767</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>44446</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44662</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44582.64112268519</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44470</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>44718.44672453704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>44853</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>44424</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>44316</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>44701</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44704.5418287037</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44525.45300925926</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>44250</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44825</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44578</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>44256</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>44711.460625</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>44887.38490740741</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44747</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>44466</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44709.48592592592</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>44709.46103009259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>44709.47613425926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44783</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44733.37920138889</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44733.38643518519</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>44804</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44722.62962962963</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44245</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>44146</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44537</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44539</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44420</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44733.3975462963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44613</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>44530</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44104</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44239</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44137</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44440</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>44425</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>44614</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>44708</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44729</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44652.50168981482</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>44153</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>44658</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>44522</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>44713</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>44522</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44882</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44446</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>44475</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>44348.90090277778</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44881.43841435185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44862</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44440</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44627</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44238</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44462</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44505</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44256</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44525.48111111111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44812.67331018519</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45335</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45202.41581018519</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44865</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44363</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44102</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44413</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>45330</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>45343.55482638889</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45008.46658564815</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44830</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>45090</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>44784</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>44326</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44536</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44813.53872685185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44881</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>45378.34151620371</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>44474</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44679</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44858</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45747.46189814815</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44830</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45365.46865740741</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44825</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45440</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45424</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45441.52587962963</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45733.69351851852</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45733.70636574074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45170</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45162</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44901.48960648148</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45356</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44246</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45307</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44144</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44266</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45107</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>45379.62061342593</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>44960</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45756</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>45443.54708333333</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45424</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44950</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45398</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45350</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45082</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45315</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45040</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>44224</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>44097</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45387.57589120371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>44846.6333912037</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45288</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45350</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>44433</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>44414.37789351852</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44530</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45190.53902777778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>44968.39174768519</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45132.64674768518</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44496</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45224</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45224</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>44251</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45741</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>44623</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45145.5899537037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45775</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>44430</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45098</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45781.83173611111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45775</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45425</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44579</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45335</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>44817</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45370</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         <v>45279</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45419</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45419</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45159</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44267</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>44517</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44553</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45365.46444444444</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>44980</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>44995.58079861111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>44976</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45029</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44837</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>44859</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>44384</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>44579</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>44525.48533564815</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44938.51252314815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>44575</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>44188</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45359.38408564815</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>44812</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>44546</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45096</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45635.46380787037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45630.56158564815</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45306</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44350</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45721.64368055556</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45452</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45149</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>44425</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45789.53918981482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>45524</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45173</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>44536</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45132</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45132.61612268518</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>44837</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>44224</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45789.54369212963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45162</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44537</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45162</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45705</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44440</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>44949</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45243</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45637.46026620371</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45624.38962962963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>44430</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>44575</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45181</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>44581</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45518.68938657407</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44477</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45160</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44995</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44515.40481481481</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>45582.36425925926</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45721.60896990741</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45721.61415509259</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44452</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45611.48289351852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45546.34533564815</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45793.50888888889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>44938.52150462963</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45335</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45335</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45329</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45329</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45603</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45603.67677083334</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45161</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>44494</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>44364</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44144</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>44719</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>44936.74096064815</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>44585.39070601852</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45114</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>44529</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44536</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44146</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44578</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>45170</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45559</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45559</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45373.48542824074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44293</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45702</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>44992</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>44748</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44813.5283449074</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45075</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44138</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44138</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44497</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>45329</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44904</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44092</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45721.61918981482</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45721.62387731481</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>44119</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44525</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45210</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45239</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>45537</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45747</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45603.67597222222</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45352</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45352</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45352</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44890</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45218</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>45801.4565162037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44140</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44839</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44840</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45660.70398148148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44153</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45166</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44432</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>45802</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44126</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45729.41755787037</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>45803.28027777778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45350.66584490741</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45393.53303240741</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45153</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44652</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45044</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44153</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45044.60363425926</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45730.74708333334</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44137</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44634</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45044.63796296297</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44525.90890046296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44525.9234375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45056</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>45061</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45187</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>45553</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45810.48511574074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45810.49662037037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>44370</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>45672</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>45730.51428240741</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45604.61385416667</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>45674</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45005.33341435185</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>45786</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>44938.65421296296</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30846,7 +30846,7 @@
         <v>45733</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44181</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>45161</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>45146</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45110</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44620</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45813</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>45813.38466435186</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45813</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45370</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45817.52033564815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45546.32984953704</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>45166</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44896</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>45261</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>45817.42873842592</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45817.40743055556</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44711.46961805555</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>45817.43488425926</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>45624.3790162037</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45798</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44649</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>44811</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44810</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>44838</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>45817.30131944444</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45817.43222222223</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44839</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44537</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>44957</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>45819.64758101852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>45820.30832175926</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>45820.56608796296</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>45819.64578703704</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45819.65145833333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>45819.66092592593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45820.5670949074</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45820</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44728.40604166667</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45819.64652777778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45819.65033564815</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>45819.66016203703</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45819.65243055556</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45819.65354166667</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45051</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>45821.34972222222</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45743.70403935185</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44944</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45166.58883101852</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45685.31189814815</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45685</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45685</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45821.36927083333</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45715.59168981481</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44200</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44475.45990740741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>44725</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>44774</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44853</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>44246</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45826.32295138889</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44397.39152777778</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45826</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45162</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44936</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44199</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44200</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44200</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44645.64319444444</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45720.51685185185</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>44858</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45831.5509837963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>45222</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>44132</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>44132</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>45461</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>44799</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>45705</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45712.63317129629</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>44199</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>44200</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44725</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45831</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>45831.55019675926</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45702</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45873.38168981481</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>44784</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45832.41319444445</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45831.54910879629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45831.55167824074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45218</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45000.36548611111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>45832.58648148148</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>45733.70386574074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>45289</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>44216</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>44992</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45741</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45713.34657407407</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45713</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45603</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>45559.48292824074</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>44489</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45547</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>44990</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44767.70469907407</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45712.46146990741</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44784</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>44846.63041666667</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45343</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45027</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45834.81833333334</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45834.9077662037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44744.68890046296</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44690</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45348</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>44966</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44893.39328703703</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>45349.71461805556</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45110</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>44607.459375</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45834.81365740741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45834.90304398148</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45365.45710648148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>44363</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>44965.50133101852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>44810</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>44812</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45258</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>44462</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>44931.84092592593</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45624</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>44958</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>44960.4335300926</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>44454</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>44452</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>44964</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>44965</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>44965</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44988</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45840.48537037037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45414.52494212963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45143</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>44974.44780092593</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45092</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44575</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45882.36824074074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45440</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45112</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>44998</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>44678</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45033</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45385</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>44235</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44491</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45602.35326388889</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45062</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45443.54967592593</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>44733.48971064815</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>45210</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45705</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>44727</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>45271</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45743.69769675926</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45743.70009259259</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>44200</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>44783</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45727.35582175926</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>44740.79188657407</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45706</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>45278</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44207</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45645.62415509259</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44209</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44755</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44620.7231712963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>45301</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45628</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>44698</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45842.38885416667</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>44977.44368055555</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45138</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>44676</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45085</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>44540.69231481481</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>44967</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>45841.33006944445</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>44375</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>45603</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45842.39219907407</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>44582.63854166667</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42321,7 +42321,7 @@
         <v>45841.40429398148</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>44382</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>45216</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45545</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
         <v>45720.84736111111</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>44858</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45685</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>44404</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>44382</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>44757</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45530</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>45224</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45205</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45715.37094907407</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43149,7 +43149,7 @@
         <v>45202.41700231482</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>44364</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>44336</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43320,7 +43320,7 @@
         <v>44425</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>45729.39240740741</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>44435.57420138889</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>44575.41842592593</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>44209</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>45729.40546296296</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>45210.7621875</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>45761</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45110</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>45202.41826388889</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45672.32315972223</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>44456</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>44425</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>44879</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45842.38351851852</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>44830</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45328</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45183</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45524</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>44089.82252314815</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45069</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>44910.40516203704</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>44475</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>44475</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45842.38688657407</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45733.61880787037</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>44200</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>44825.65760416666</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>44110</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45706</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>44943</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44943</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45076</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45327</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>45229</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>44463</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44462</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>44960</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>44970</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45272.4568287037</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>44358</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45660</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>44462</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45419</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45878,7 +45878,7 @@
         <v>44790.56490740741</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>44960</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45844.94479166667</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46049,7 +46049,7 @@
         <v>45844.94641203704</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>44880</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45702</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>44650</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>44118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>44179.46130787037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>44837</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>44879</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>44879</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>44419</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45001</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>44278</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>44278</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>44245</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44938.45053240741</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45686</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>44199</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47053,7 +47053,7 @@
         <v>45058.61591435185</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>44916.67027777778</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45733.69909722222</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45019.65358796297</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>44339</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>44812</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>44199</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>44199</v>
       </c>
       <c r="C767" s="1" t="n">
-      